--- a/results/05_transient_transcription_output/905/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/905/Top_Excel_with_OCR_Results.xlsx
@@ -639,7 +639,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">2241
 </t>
         </is>
       </c>
@@ -651,7 +651,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
@@ -669,7 +669,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
@@ -680,15 +680,24 @@
         </is>
       </c>
       <c r="M4" s="2" t="n"/>
-      <c r="N4" s="2" t="n"/>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="P4" s="2" t="n"/>
-      <c r="Q4" s="2" t="n"/>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>431</t>
+        </is>
+      </c>
       <c r="R4" s="2" t="n"/>
       <c r="S4" s="2" t="inlineStr">
         <is>
@@ -696,16 +705,21 @@
 </t>
         </is>
       </c>
-      <c r="T4" s="2" t="n"/>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">851
+</t>
+        </is>
+      </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">803
 </t>
         </is>
       </c>
@@ -717,13 +731,13 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">861
 </t>
         </is>
       </c>
@@ -760,18 +774,27 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4380</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">35
@@ -780,19 +803,15 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17 5
-</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">99
+211
+</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -804,11 +823,16 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="n"/>
+          <t xml:space="preserve">900
+</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">248
@@ -817,7 +841,8 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">213
+</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -828,7 +853,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">743
+          <t xml:space="preserve">943
 </t>
         </is>
       </c>
@@ -889,7 +914,7 @@
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -901,7 +926,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
@@ -919,33 +944,40 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1725
-</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="n"/>
+          <t xml:space="preserve">16495171
+178
+2 2 4221
+</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1416
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -963,7 +995,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>083</t>
+          <t>783</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -971,26 +1003,36 @@
           <t>691</t>
         </is>
       </c>
-      <c r="U6" s="2" t="n"/>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="Y6" s="2" t="n"/>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">21
@@ -1011,24 +1053,20 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2744
-</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+          <t xml:space="preserve">344
+</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -1040,7 +1078,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -1058,7 +1096,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -1070,20 +1108,25 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">1729
 </t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="n"/>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">940
+</t>
+        </is>
+      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -1095,7 +1138,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">2287
 </t>
         </is>
       </c>
@@ -1131,7 +1174,7 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -1143,7 +1186,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -1161,25 +1204,25 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2602
+          <t xml:space="preserve">16024
 </t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -1203,44 +1246,39 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">093
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4580</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118628
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">818
+</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="n"/>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8821
+          <t xml:space="preserve">898
 </t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2465
-</t>
+          <t>4451</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
@@ -1257,13 +1295,13 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">871
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
@@ -1285,8 +1323,18 @@
 </t>
         </is>
       </c>
-      <c r="Y8" s="2" t="n"/>
-      <c r="Z8" s="2" t="n"/>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">860
+</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>5</t>
@@ -1300,30 +1348,17 @@
         </is>
       </c>
       <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">829
-</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>778</t>
-        </is>
-      </c>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">617
+          <t xml:space="preserve">627
 </t>
         </is>
       </c>
@@ -1341,49 +1376,53 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
-</t>
+          <t>371</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8145
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">982
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr"/>
+          <t xml:space="preserve">882
+</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t xml:space="preserve">1271
+</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>710</t>
         </is>
       </c>
       <c r="S9" s="2" t="n"/>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1842
+          <t xml:space="preserve">3892
 </t>
         </is>
       </c>
@@ -1395,7 +1434,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">989
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
@@ -1407,11 +1446,16 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="Y9" s="2" t="n"/>
-      <c r="Z9" s="2" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="n"/>
       <c r="AA9" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1426,27 +1470,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22404
-</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="n"/>
-      <c r="F10" s="2" t="n"/>
+          <t xml:space="preserve">1464
+</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4465227
+8179171
+</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2282891
+181
+</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82828
+199812
+</t>
+        </is>
+      </c>
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="n"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
       <c r="J10" s="2" t="n"/>
-      <c r="K10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">792871272
+1
+</t>
+        </is>
+      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="n"/>
-      <c r="N10" s="2" t="n"/>
-      <c r="O10" s="2" t="n"/>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">845
+</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">784
+</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">94
+2
+</t>
+        </is>
+      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">9
@@ -1455,17 +1544,38 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="n"/>
-      <c r="S10" s="2" t="inlineStr"/>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7424
+1111
+</t>
+        </is>
+      </c>
       <c r="T10" s="2" t="n"/>
       <c r="U10" s="2" t="n"/>
       <c r="V10" s="2" t="n"/>
-      <c r="W10" s="2" t="n"/>
-      <c r="X10" s="2" t="n"/>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77
+</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4451
+</t>
+        </is>
+      </c>
       <c r="Y10" s="2" t="n"/>
       <c r="Z10" s="2" t="n"/>
       <c r="AA10" t="inlineStr">
@@ -1482,31 +1592,15 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
-</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">284
-</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1661
-</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">295
-</t>
-        </is>
-      </c>
+          <t>4985</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -1516,50 +1610,46 @@
 </t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">821
-</t>
-        </is>
-      </c>
+      <c r="I11" s="2" t="n"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="n"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77718
+6222
+</t>
+        </is>
+      </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">1691
 </t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1906
+          <t xml:space="preserve">231
+24721195
 </t>
         </is>
       </c>
       <c r="P11" s="2" t="n"/>
       <c r="Q11" s="2" t="n"/>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">929
-</t>
-        </is>
-      </c>
+      <c r="R11" s="2" t="n"/>
       <c r="S11" s="2" t="n"/>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">768
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -1571,31 +1661,31 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1981
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">1865
 </t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2066
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">8960
 </t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
@@ -1613,7 +1703,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2996
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
@@ -1634,75 +1724,71 @@
           <t>313</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">977
+</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">2911
 </t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t xml:space="preserve">12
+</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">1661
 </t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">2415
 </t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2390
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
@@ -1720,19 +1806,19 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8220
+          <t xml:space="preserve">2280
 </t>
         </is>
       </c>
@@ -1744,7 +1830,8 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">40
+</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1791,7 +1878,8 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">159
+1109
 </t>
         </is>
       </c>
@@ -1803,32 +1891,32 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1394
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="K13" s="2" t="n"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
@@ -1852,7 +1940,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -1864,7 +1952,7 @@
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -1876,13 +1964,13 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">2219
 </t>
         </is>
       </c>
@@ -1912,13 +2000,14 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2238
+          <t xml:space="preserve">3238
 </t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>7285</t>
+          <t xml:space="preserve">275
+</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1930,52 +2019,49 @@
       <c r="F14" s="2" t="n"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>051</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">05
+</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="n"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1771
 </t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>61</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
-</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr"/>
+          <t xml:space="preserve">921
+</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">244
@@ -1984,18 +2070,19 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0114
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4271</t>
+          <t xml:space="preserve">237
+</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
@@ -2019,16 +2106,11 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="Y14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">958
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="n"/>
       <c r="Z14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">09
@@ -2049,7 +2131,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2600
+          <t xml:space="preserve">2666
 </t>
         </is>
       </c>
@@ -2065,75 +2147,55 @@
 </t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+      <c r="F15" s="2" t="n"/>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1714
-</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
+          <t xml:space="preserve">2324
+</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="n"/>
+      <c r="O15" s="2" t="n"/>
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">26
 </t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="n"/>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">896
-</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">2410
 </t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
@@ -2146,7 +2208,7 @@
       <c r="T15" s="2" t="n"/>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -2162,10 +2224,15 @@
 </t>
         </is>
       </c>
-      <c r="X15" s="2" t="n"/>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">958
+</t>
+        </is>
+      </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -2189,7 +2256,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89348
+          <t xml:space="preserve">348
 </t>
         </is>
       </c>
@@ -2207,13 +2274,13 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29225
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -2235,20 +2302,16 @@
 </t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="K16" s="2" t="n"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
@@ -2260,37 +2323,38 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>1584</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">414
 </t>
         </is>
       </c>
       <c r="S16" s="2" t="n"/>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">21214
+7922
+</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
@@ -2308,7 +2372,7 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">803
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -2320,8 +2384,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2336,71 +2399,62 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>156468</t>
-        </is>
-      </c>
+      <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1372</t>
+          <t>33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>561</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1099
-</t>
-        </is>
-      </c>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="n"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>060</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">790
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">853
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>865594</t>
-        </is>
-      </c>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="n"/>
       <c r="P17" s="2" t="inlineStr">
         <is>
           <t>614</t>
@@ -2408,22 +2462,26 @@
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr"/>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">744
+981
+</t>
+        </is>
+      </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="T17" s="2" t="n"/>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3591
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2434,18 +2492,18 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">989
-</t>
+          <t>96121</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>097</t>
+          <t xml:space="preserve">8203
+</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -2470,34 +2528,40 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2681
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1711
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8917
+          <t xml:space="preserve">9917
 </t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2971
+          <t xml:space="preserve">971
 </t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>446</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">30
@@ -2513,19 +2577,18 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1171
-</t>
+          <t>85341</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 99
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">932
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -2537,19 +2600,19 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>03</t>
         </is>
       </c>
       <c r="R18" s="2" t="n"/>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2291
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1881
+          <t xml:space="preserve">1851
 </t>
         </is>
       </c>
@@ -2561,25 +2624,25 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">1097
 </t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6574
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -2615,27 +2678,31 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr"/>
+          <t xml:space="preserve">77718
+273
+</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77
+</t>
+        </is>
+      </c>
       <c r="H19" s="2" t="n"/>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -2647,18 +2714,14 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">871
 </t>
         </is>
       </c>
@@ -2682,7 +2745,7 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
@@ -2694,35 +2757,35 @@
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">2691
 </t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">835
-</t>
-        </is>
-      </c>
-      <c r="Z19" s="2" t="n"/>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
           <t>12</t>
@@ -2735,40 +2798,35 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
+      <c r="C20" s="2" t="n"/>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1621
 </t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1067
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="H20" s="2" t="n"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">5454824
 </t>
         </is>
       </c>
@@ -2792,25 +2850,25 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -2822,44 +2880,44 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">2685
+</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="n"/>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr"/>
+          <t xml:space="preserve">31
+</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">729
+</t>
+        </is>
+      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">2341
 </t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">835
 </t>
         </is>
       </c>
@@ -2883,72 +2941,66 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12534
+          <t xml:space="preserve">2534
 </t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">883
 </t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0164</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">828127
+160
+745414119
+</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="n"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">591
-</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">31
+</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t xml:space="preserve">283
+</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -2959,7 +3011,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">67
 </t>
         </is>
       </c>
@@ -2977,11 +3029,17 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1898
-</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="n"/>
+          <t xml:space="preserve">47
+</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+1 1
+</t>
+        </is>
+      </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">31
@@ -2990,25 +3048,25 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">1209
 </t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">1991
 </t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">736
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
@@ -3032,7 +3090,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">53349
+          <t xml:space="preserve">2661
 </t>
         </is>
       </c>
@@ -3044,32 +3102,33 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92925
-</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">90
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">255
+</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="n"/>
       <c r="H22" s="2" t="n"/>
-      <c r="I22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">44282
+</t>
+        </is>
+      </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">23
+77
 </t>
         </is>
       </c>
@@ -3081,13 +3140,13 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -3099,7 +3158,8 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">12
+2
 </t>
         </is>
       </c>
@@ -3115,39 +3175,31 @@
 </t>
         </is>
       </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
+      <c r="S22" s="2" t="n"/>
+      <c r="T22" s="2" t="n"/>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1890
+          <t xml:space="preserve">449
+190
 </t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8232
+          <t xml:space="preserve">124
+1856
 </t>
         </is>
       </c>
@@ -3177,7 +3229,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15486
+          <t xml:space="preserve">392
 </t>
         </is>
       </c>
@@ -3195,38 +3247,28 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">3106
 </t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">749
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="n"/>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>6163</t>
-        </is>
-      </c>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="n"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">180
@@ -3235,49 +3277,49 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1171
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">2512
 </t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3931
+          <t xml:space="preserve">400
 </t>
         </is>
       </c>
@@ -3287,18 +3329,8 @@
 </t>
         </is>
       </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">231
-</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">998
-</t>
-        </is>
-      </c>
+      <c r="V23" s="2" t="n"/>
+      <c r="W23" s="2" t="n"/>
       <c r="X23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">196
@@ -3331,133 +3363,115 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>309</t>
+          <t xml:space="preserve">586
+</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>7376</t>
+          <t>37</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>8510</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11159
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>572</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8692</t>
+          <t xml:space="preserve">491
+</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>633</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2381
-</t>
+          <t>752</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">787
+          <t xml:space="preserve">937
 </t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>371</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
-</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
+          <t xml:space="preserve">163
+</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="n"/>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>1705</t>
-        </is>
-      </c>
-      <c r="Y24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">008
-</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="n"/>
       <c r="Z24" s="2" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
@@ -3473,7 +3487,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2798
+          <t xml:space="preserve">397
 </t>
         </is>
       </c>
@@ -3485,50 +3499,65 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1701
+          <t xml:space="preserve">1791
 </t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>1448</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="n"/>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>984</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="n"/>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">181
+</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1741
-</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr"/>
+          <t xml:space="preserve">878
+</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6
+</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9380
+          <t xml:space="preserve">381
 </t>
         </is>
       </c>
@@ -3546,18 +3575,19 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t xml:space="preserve">38
+</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">825
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
@@ -3569,31 +3599,26 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="Y25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">750
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="n"/>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -3611,62 +3636,51 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3414
+          <t xml:space="preserve">2798
 </t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
+          <t>948</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="n"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="n"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">174
 </t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr"/>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -3678,7 +3692,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -3690,43 +3704,44 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9146
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
+          <t xml:space="preserve">865
 </t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>016</t>
+          <t xml:space="preserve">211
+</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">18020
 </t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
@@ -3748,7 +3763,12 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3414
+</t>
+        </is>
+      </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">248
@@ -3757,44 +3777,65 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">792
+67
 </t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="n"/>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+1119
+</t>
+        </is>
+      </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="n"/>
-      <c r="L27" s="2" t="inlineStr"/>
+          <t xml:space="preserve">37
+</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">970
@@ -3803,56 +3844,60 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr"/>
+          <t>411</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">696
+          <t xml:space="preserve">839
 </t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">824
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">836
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
@@ -3876,7 +3921,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
+          <t xml:space="preserve">3700
 </t>
         </is>
       </c>
@@ -3886,18 +3931,8 @@
 </t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2817
-</t>
-        </is>
-      </c>
+      <c r="E28" s="2" t="n"/>
+      <c r="F28" s="2" t="n"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">101
@@ -3926,12 +3961,13 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t xml:space="preserve">167
+</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3943,66 +3979,67 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>855</t>
+          <t xml:space="preserve">255
+</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2181
+</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">897
+</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">696
+</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">188
 </t>
         </is>
       </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7467
-</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">864
-</t>
-        </is>
-      </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">785
+          <t xml:space="preserve">83836
 </t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -4020,25 +4057,21 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3436
+          <t xml:space="preserve">4536
 </t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">65
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4007
+263
+</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n"/>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">8414
 </t>
         </is>
       </c>
@@ -4050,12 +4083,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1499</t>
+          <t>141</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">331
+          <t xml:space="preserve">335
 </t>
         </is>
       </c>
@@ -4067,7 +4100,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
@@ -4079,20 +4112,20 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">6041
+151
 </t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
+          <t>05840</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4109,49 +4142,49 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">17272
 </t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">866
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
+          <t xml:space="preserve">747
 </t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0612
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">752
 </t>
         </is>
       </c>
@@ -4175,37 +4208,36 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1788</t>
+          <t xml:space="preserve">3436
+</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1211
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">064
 </t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">707
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -4222,7 +4254,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -4234,43 +4266,48 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>551</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>865</t>
+          <t xml:space="preserve">865
+</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="n"/>
+          <t xml:space="preserve">2280
+</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1094
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">815
+</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -4281,25 +4318,25 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1618
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>881</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -4322,13 +4359,13 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23577
+          <t xml:space="preserve">17884
 </t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
@@ -4340,25 +4377,25 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">451111
+          <t xml:space="preserve">501
 </t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1830
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
@@ -4368,7 +4405,12 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 3
+</t>
+        </is>
+      </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">859
@@ -4377,39 +4419,42 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2018
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>85431</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr"/>
+          <t xml:space="preserve">45845
+</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1 48
+</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>018</t>
+        </is>
+      </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2191
+          <t xml:space="preserve">024
 </t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">784
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -4420,31 +4465,29 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">999
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>002</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4461,13 +4504,13 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2666
+          <t xml:space="preserve">357
 </t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
@@ -4479,84 +4522,88 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">24
+77
 </t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+777
+</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">909
+</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">100
 </t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16811
-</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">491
 </t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9780
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -4568,26 +4615,26 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr"/>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">834
 </t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -4605,25 +4652,25 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14008
+          <t xml:space="preserve">2666
 </t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">73
 </t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
@@ -4646,12 +4693,7 @@
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1297
-</t>
-        </is>
-      </c>
+      <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">190
@@ -4660,79 +4702,85 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">011
+          <t xml:space="preserve">1616
 </t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">204
 </t>
         </is>
       </c>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">774
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
+          <t xml:space="preserve">9461
 </t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -4750,13 +4798,13 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12502
+          <t xml:space="preserve">4068
 </t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -4768,38 +4816,39 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">417
 </t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1156
-</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr"/>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7777
+262
+</t>
+        </is>
+      </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="n"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
@@ -4811,7 +4860,7 @@
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -4823,61 +4872,61 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">748
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">860
 </t>
         </is>
       </c>
@@ -4901,7 +4950,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2688
+          <t xml:space="preserve">356
 </t>
         </is>
       </c>
@@ -4919,13 +4968,13 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
@@ -4937,83 +4986,78 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">37
 </t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>001</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>450</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8200
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1837
+</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr"/>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">2198
 </t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">760
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -5025,7 +5069,7 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">011
+          <t xml:space="preserve">606
 </t>
         </is>
       </c>
@@ -5037,7 +5081,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -5055,7 +5099,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3568
+          <t xml:space="preserve">4688
 </t>
         </is>
       </c>
@@ -5067,35 +5111,37 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>484</t>
+          <t xml:space="preserve">207
+</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t xml:space="preserve">82
+</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -5107,83 +5153,76 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr"/>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n"/>
+      <c r="N36" s="2" t="n"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8006
+</t>
+        </is>
+      </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>9641</t>
+          <t xml:space="preserve">228
+</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">760
+</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="n"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">208
 </t>
         </is>
       </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">602
-</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2808
-</t>
-        </is>
-      </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>06</t>
+          <t xml:space="preserve">116
+</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
+          <t xml:space="preserve">956
 </t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5200,30 +5239,27 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>1643</t>
+          <t xml:space="preserve">358
+</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>174</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>89</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1071
-</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>083</t>
-        </is>
-      </c>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
           <t>806</t>
@@ -5231,91 +5267,91 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>313</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>7361</t>
+          <t xml:space="preserve">16
+</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>883</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr"/>
-      <c r="N37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8980
+          <t xml:space="preserve">70
 </t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">45
+</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>9611</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">208
 </t>
         </is>
       </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1123
-</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">991
-</t>
-        </is>
-      </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">038
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2894
-</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="n"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">981
+2248
 </t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">985
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
+          <t xml:space="preserve">77
+181 1
 </t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -5339,32 +5375,31 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
+          <t xml:space="preserve">6432
 </t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">863
+          <t xml:space="preserve">9637
 </t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2141
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>085</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -5375,12 +5410,24 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2011
-</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="n"/>
-      <c r="K38" s="2" t="inlineStr"/>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5247
+2272
+1
+</t>
+        </is>
+      </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">177
@@ -5389,42 +5436,45 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr"/>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="n"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>796</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr"/>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2081
+          <t xml:space="preserve">638
 </t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">771
-</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="n"/>
+          <t>558</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">196
@@ -5433,18 +5483,19 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10921
+          <t xml:space="preserve">14441
+346
 </t>
         </is>
       </c>
       <c r="X38" s="2" t="n"/>
-      <c r="Y38" s="2" t="n"/>
-      <c r="Z38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">44
+</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="n"/>
       <c r="AA38" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -5459,83 +5510,99 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">1
+1 23
 </t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr"/>
+          <t xml:space="preserve">414
+</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">971
+</t>
+        </is>
+      </c>
       <c r="H39" s="2" t="n"/>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">37
+</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">188
 </t>
         </is>
       </c>
-      <c r="M39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">171
+</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="n"/>
-      <c r="P39" s="2" t="n"/>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr"/>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">1181
 </t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">350
 </t>
         </is>
       </c>
@@ -5547,7 +5614,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">809
+          <t xml:space="preserve">1851
 </t>
         </is>
       </c>
@@ -5563,12 +5630,7 @@
 </t>
         </is>
       </c>
-      <c r="Z39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
+      <c r="Z39" s="2" t="n"/>
       <c r="AA39" t="inlineStr">
         <is>
           <t>26</t>
@@ -5595,7 +5657,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -5605,17 +5667,11 @@
 </t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
+      <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="n"/>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -5630,60 +5686,53 @@
 </t>
         </is>
       </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>438</t>
-        </is>
-      </c>
+      <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="n"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">2852
 </t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">21626
 </t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t xml:space="preserve">231 1
+</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">721
 </t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2012
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
@@ -5713,7 +5762,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
@@ -5731,7 +5780,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3590
+          <t xml:space="preserve">2864
 </t>
         </is>
       </c>
@@ -5743,56 +5792,57 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>015</t>
+          <t xml:space="preserve">297
+</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">196
+111
+</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">58
+</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">090
+</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="n"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">18
 </t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">58
-</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr"/>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">153
-</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1186
-</t>
-        </is>
-      </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">762
+          <t xml:space="preserve">766
 </t>
         </is>
       </c>
@@ -5804,31 +5854,29 @@
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">1951
 </t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1204
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">614
-</t>
+          <t>7444</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -5846,13 +5894,13 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">805
+          <t xml:space="preserve">705
 </t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -5876,75 +5924,82 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">3590
 </t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr"/>
+          <t xml:space="preserve">2135
+</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
       <c r="H42" s="2" t="n"/>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t xml:space="preserve">39
+</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1177
-</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t xml:space="preserve">29
+2
+</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="n"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9271249
+157
+</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1316
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
@@ -5956,22 +6011,17 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">855
-</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">141
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">579
+</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="n"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">222
@@ -5980,13 +6030,13 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">9134
 </t>
         </is>
       </c>
@@ -5996,7 +6046,12 @@
 </t>
         </is>
       </c>
-      <c r="Z42" s="2" t="n"/>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">721
+</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>29</t>
@@ -6011,13 +6066,14 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>7345</t>
+          <t xml:space="preserve">276
+</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -6028,93 +6084,116 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5925
-</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">697
-</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="n"/>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">65
+</t>
+        </is>
+      </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11615
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr"/>
+          <t xml:space="preserve">711797
+127
+</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+118
+</t>
+        </is>
+      </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">798
 </t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr"/>
+          <t xml:space="preserve">2031
+</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>777</t>
+          <t xml:space="preserve">555
+</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1088
+          <t xml:space="preserve">216868
 </t>
         </is>
       </c>
       <c r="V43" s="2" t="n"/>
-      <c r="W43" s="2" t="inlineStr"/>
-      <c r="X43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="n"/>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>377</t>
-        </is>
-      </c>
-      <c r="Z43" s="2" t="n"/>
+          <t xml:space="preserve">236
+</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>577</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>30</t>
@@ -6129,119 +6208,121 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">24
+60292929572
 </t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="n"/>
-      <c r="G44" s="2" t="n"/>
-      <c r="H44" s="2" t="n"/>
+          <t xml:space="preserve">773
+</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1577
+</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">55
+</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">697
+</t>
+        </is>
+      </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1614
+          <t xml:space="preserve">1642
+24749414
 </t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
+          <t xml:space="preserve">1878
 </t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">796
-</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">42
+</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="n"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4055
-</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">291
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">727
+</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr"/>
+      <c r="Q44" s="2" t="inlineStr"/>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">728
 </t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
+          <t xml:space="preserve">7773
 </t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65566
-</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">028
+</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="n"/>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="X44" s="2" t="n"/>
+          <t xml:space="preserve">985
+</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">836
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
@@ -6260,11 +6341,15 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3679
-</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="n"/>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">397
+</t>
+        </is>
+      </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">164
@@ -6273,13 +6358,14 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>451</t>
+          <t xml:space="preserve">1791287
+</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -6290,19 +6376,19 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -6314,11 +6400,17 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="n"/>
+          <t xml:space="preserve">79
+</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4
+1
+</t>
+        </is>
+      </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">811
@@ -6327,35 +6419,61 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>341</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="n"/>
-      <c r="R45" s="2" t="n"/>
-      <c r="S45" s="2" t="inlineStr"/>
-      <c r="T45" s="2" t="inlineStr"/>
+          <t>521</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">251
+</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2628
+</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6
+</t>
+        </is>
+      </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>4638</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">4224574
+1
 </t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="X45" s="2" t="inlineStr"/>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+1
+</t>
+        </is>
+      </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -6374,84 +6492,112 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="n"/>
-      <c r="E46" s="2" t="inlineStr"/>
-      <c r="F46" s="2" t="n"/>
-      <c r="G46" s="2" t="inlineStr"/>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1817857
+1 1
+1
+3
+6
+</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">526
+</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">16
 </t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="2" t="inlineStr"/>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="n"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr"/>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="n"/>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="n"/>
+      <c r="S46" s="2" t="inlineStr"/>
       <c r="T46" s="2" t="n"/>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
-      <c r="V46" s="2" t="n"/>
-      <c r="W46" s="2" t="inlineStr">
-        <is>
           <t xml:space="preserve">1
 </t>
         </is>
       </c>
-      <c r="X46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1189
+</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="n"/>
+      <c r="X46" s="2" t="n"/>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">1145
 </t>
         </is>
       </c>
@@ -6470,26 +6616,57 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15 11
-</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10280
-</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1048
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">324 7
+</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">727
+</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6 9
+1
+1191
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/905/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/905/Top_Excel_with_OCR_Results.xlsx
@@ -624,43 +624,41 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23898
+</t>
+        </is>
+      </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">1283
 </t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">1158
 </t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2241
+          <t xml:space="preserve">1221
 </t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">55
@@ -669,42 +667,51 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="n"/>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0168
+</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="n"/>
+          <t xml:space="preserve">900
+</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>431</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="n"/>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">237
+</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="n"/>
       <c r="T4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">851
@@ -719,7 +726,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">803
+          <t xml:space="preserve">28208
 </t>
         </is>
       </c>
@@ -731,13 +738,13 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">861
+          <t xml:space="preserve">2861
 </t>
         </is>
       </c>
@@ -759,7 +766,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n"/>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14286
+</t>
+        </is>
+      </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">282
@@ -774,27 +786,23 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4380</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1258
+</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="n"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">35
@@ -803,15 +811,14 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-211
-</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1223
+</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -823,38 +830,37 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">1931
 </t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">1694
 </t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">12248
 </t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">013
 </t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">111012
 </t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">943
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -871,8 +877,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
@@ -914,19 +919,19 @@
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">1270
 </t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">8261
 </t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">1269
 </t>
         </is>
       </c>
@@ -938,49 +943,42 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">098
 </t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
-</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="n"/>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16495171
-178
-2 2 4221
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">107
+</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="n"/>
       <c r="Q6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">268
@@ -989,41 +987,42 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">2203
 </t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>783</t>
+          <t xml:space="preserve">243
+</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>64</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
@@ -1051,22 +1050,22 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">344
-</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">282
+</t>
+        </is>
+      </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">0202
 </t>
         </is>
       </c>
@@ -1078,7 +1077,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -1096,85 +1095,65 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1279
+</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1698
+</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">898
+</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">22
 </t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1729
-</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">940
-</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">273
-</t>
-        </is>
-      </c>
+      <c r="Q7" s="2" t="n"/>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2287
-</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">227
+</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="n"/>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">687
-</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">688
+</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr"/>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">1208
 </t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
@@ -1186,7 +1165,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -1202,33 +1181,28 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16024
-</t>
-        </is>
-      </c>
+      <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -1246,68 +1220,69 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr"/>
+          <t xml:space="preserve">33
+</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">141
+</t>
+        </is>
+      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="n"/>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1082
+</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
+          <t xml:space="preserve">882
 </t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>4451</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1212
+</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="n"/>
       <c r="R8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">228
 </t>
         </is>
       </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
+      <c r="S8" s="2" t="n"/>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">881
 </t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">1096
 </t>
         </is>
       </c>
@@ -1331,7 +1306,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -1353,13 +1328,13 @@
       <c r="F9" s="2" t="n"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t xml:space="preserve">2598
+</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">627
-</t>
+          <t>7221</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1370,36 +1345,31 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>310</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">75
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">845
+</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="n"/>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
+          <t xml:space="preserve">342201
 </t>
         </is>
       </c>
@@ -1408,54 +1378,41 @@
           <t>24</t>
         </is>
       </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1271
-</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>710</t>
-        </is>
-      </c>
+      <c r="Q9" s="2" t="n"/>
+      <c r="R9" s="2" t="n"/>
       <c r="S9" s="2" t="n"/>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3892
+          <t xml:space="preserve">3842
 </t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">385
-</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">89
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">19385
+</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="n"/>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="X9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t xml:space="preserve">9271031
+</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="n"/>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="Z9" s="2" t="n"/>
+          <t xml:space="preserve">194451
+</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1470,114 +1427,78 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1464
-</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4465227
-8179171
-</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2282891
-181
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4281
+</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82828
-199812
-</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">825
+</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1181
+</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">135
+</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="n"/>
       <c r="J10" s="2" t="n"/>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">792871272
-1
-</t>
-        </is>
-      </c>
+      <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">845
-</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">784
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">8220171
+</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="n"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-2
-</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">9061
+</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="n"/>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7424
-1111
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">299
+</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="n"/>
+      <c r="S10" s="2" t="n"/>
       <c r="T10" s="2" t="n"/>
-      <c r="U10" s="2" t="n"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77
+</t>
+        </is>
+      </c>
       <c r="V10" s="2" t="n"/>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">77
-</t>
-        </is>
-      </c>
-      <c r="X10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4451
-</t>
-        </is>
-      </c>
+      <c r="W10" s="2" t="n"/>
+      <c r="X10" s="2" t="n"/>
       <c r="Y10" s="2" t="n"/>
-      <c r="Z10" s="2" t="n"/>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">251
+</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1592,100 +1513,129 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4985</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n"/>
-      <c r="E11" s="2" t="n"/>
-      <c r="F11" s="2" t="n"/>
+          <t xml:space="preserve">12996
+</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1265
+</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="n"/>
+          <t xml:space="preserve">1240
+</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr"/>
+          <t xml:space="preserve">2217
+</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">77718
-6222
-</t>
+          <t>4168</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1691
+          <t xml:space="preserve">1270
 </t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">231
-24721195
-</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="n"/>
-      <c r="Q11" s="2" t="n"/>
-      <c r="R11" s="2" t="n"/>
-      <c r="S11" s="2" t="n"/>
+          <t xml:space="preserve">1181
+</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="n"/>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2660
+</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">215
+</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2290
+</t>
+        </is>
+      </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">684
 </t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1217
+</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">198
 </t>
         </is>
       </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1865
-</t>
-        </is>
-      </c>
-      <c r="X11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">266
-</t>
-        </is>
-      </c>
-      <c r="Y11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8960
-</t>
-        </is>
-      </c>
+      <c r="X11" s="2" t="n"/>
+      <c r="Y11" s="2" t="n"/>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -1703,134 +1653,138 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
+          <t xml:space="preserve">23436
 </t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>313</t>
+          <t xml:space="preserve">223
+</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">977
-</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="inlineStr"/>
+          <t xml:space="preserve">291
+</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">1284
 </t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2911
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">1036
 </t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1661
+          <t xml:space="preserve">1921
 </t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2415
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">684
+          <t xml:space="preserve">1930
 </t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">1215
 </t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2280
-</t>
-        </is>
-      </c>
-      <c r="Y12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">845
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">829
+</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="n"/>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -1848,19 +1802,19 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3436
+          <t xml:space="preserve">23238
 </t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -1870,119 +1824,107 @@
 </t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">91
-</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
-1109
-</t>
-        </is>
-      </c>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="n"/>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n"/>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">1169
 </t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">1815
 </t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">2164
 </t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">1994
 </t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2219
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">891
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
@@ -2000,101 +1942,105 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3238
+          <t xml:space="preserve">2600
 </t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="n"/>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">05
-</t>
-        </is>
-      </c>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n"/>
       <c r="H14" s="2" t="n"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">2212
 </t>
         </is>
       </c>
       <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1771
+          <t xml:space="preserve">1183
 </t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1189
+</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">896
 </t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">1958
 </t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
@@ -2106,14 +2052,14 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="Y14" s="2" t="n"/>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -2131,114 +2077,130 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2666
+          <t xml:space="preserve">23348
 </t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="n"/>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">225
+</t>
+        </is>
+      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2324
-</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="n"/>
-      <c r="I15" s="2" t="n"/>
+          <t xml:space="preserve">1017
+</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1144
+</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">10914
+</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="n"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">1172
 </t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="n"/>
-      <c r="O15" s="2" t="n"/>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">940
+</t>
+        </is>
+      </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2410
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">2214
 </t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="n"/>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1993
+</t>
+        </is>
+      </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="n"/>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">958
+          <t xml:space="preserve">1060
 </t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
@@ -2256,135 +2218,123 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">348
+          <t xml:space="preserve">101618
 </t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">1348
 </t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">1099
 </t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">14814
 </t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">720
 </t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">1108
 </t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="n"/>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118126
+</t>
+        </is>
+      </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">828
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">888
+</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n"/>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>86531</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1584</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">414
-</t>
-        </is>
-      </c>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="n"/>
+      <c r="R16" s="2" t="n"/>
       <c r="S16" s="2" t="n"/>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21214
-7922
-</t>
+          <t>4196</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
+          <t xml:space="preserve">133591
 </t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">11018
 </t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">969
 </t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">1097
 </t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">4574
 </t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">104
+</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2402,111 +2352,65 @@
       <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t xml:space="preserve">268
+</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>666</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="n"/>
+          <t xml:space="preserve">19113
+</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>060</t>
+          <t xml:space="preserve">8171
+</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="n"/>
+      <c r="M17" s="2" t="n"/>
+      <c r="N17" s="2" t="n"/>
       <c r="O17" s="2" t="n"/>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>614</t>
-        </is>
-      </c>
+      <c r="P17" s="2" t="n"/>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">744
-981
-</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>7556</t>
-        </is>
-      </c>
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="n"/>
+      <c r="S17" s="2" t="n"/>
       <c r="T17" s="2" t="n"/>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+      <c r="U17" s="2" t="n"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1019
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96121</t>
-        </is>
-      </c>
-      <c r="X17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8203
-</t>
-        </is>
-      </c>
-      <c r="Y17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="n"/>
+      <c r="Y17" s="2" t="n"/>
       <c r="Z17" s="2" t="n"/>
       <c r="AA17" t="inlineStr">
         <is>
@@ -2522,133 +2426,114 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3124
+          <t xml:space="preserve">9546
 </t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9917
+          <t xml:space="preserve">2209
 </t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">971
+          <t xml:space="preserve">1167
 </t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1150
+</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1082
 </t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>85341</t>
+          <t xml:space="preserve">168
+</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">814
 </t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="n"/>
+          <t xml:space="preserve">1267
+</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2128
+</t>
+        </is>
+      </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1851
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1239
+</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="n"/>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
+          <t xml:space="preserve">1247
 </t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1097
-</t>
-        </is>
-      </c>
-      <c r="X18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1069
+</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="n"/>
+      <c r="X18" s="2" t="n"/>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">835
 </t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -2667,125 +2552,116 @@
       <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t xml:space="preserve">274
+</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">77718
-273
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr"/>
+          <t xml:space="preserve">279
+</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">089
+</t>
+        </is>
+      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">871
+          <t xml:space="preserve">940
 </t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">665
-</t>
-        </is>
-      </c>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="n"/>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2691
-</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="n"/>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="Z19" s="2" t="inlineStr"/>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">76
+</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>12</t>
@@ -2801,129 +2677,103 @@
       <c r="C20" s="2" t="n"/>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1621
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n"/>
       <c r="H20" s="2" t="n"/>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5454824
-</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
-      </c>
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="2" t="n"/>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="n"/>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2685
-</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="n"/>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1247
+</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="n"/>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">729
+          <t xml:space="preserve">1231
 </t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2341
-</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="n"/>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">835
+          <t xml:space="preserve">938
 </t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -2941,138 +2791,113 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2534
+          <t xml:space="preserve">12848
 </t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">883
-</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">90
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">225
+</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="n"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">828127
-160
-745414119
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="I21" s="2" t="n"/>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="n"/>
+      <c r="J21" s="2" t="n"/>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">235
+</t>
+        </is>
+      </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">283
-</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">970
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="n"/>
+      <c r="O21" s="2" t="n"/>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
-</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-1 1
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1226
+</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="n"/>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">2262
 </t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1209
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1991
+          <t xml:space="preserve">0206
 </t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>961</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -3090,45 +2915,55 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2661
+          <t xml:space="preserve">23392
 </t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>130</t>
+          <t xml:space="preserve">170
+</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="n"/>
-      <c r="H22" s="2" t="n"/>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44282
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-77
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -3140,46 +2975,49 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1171
+</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="n"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-2
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="n"/>
-      <c r="T22" s="2" t="n"/>
+          <t xml:space="preserve">215
+</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1236
+</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
@@ -3191,27 +3029,25 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">449
-190
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-1856
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
+          <t xml:space="preserve">691
 </t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -3227,128 +3063,91 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">392
-</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">276
-</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3106
-</t>
-        </is>
-      </c>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="2" t="n"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="n"/>
+          <t>5161</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">748
+</t>
+        </is>
+      </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">11212
+</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="n"/>
+          <t xml:space="preserve">1699
+</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">904
 </t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>8894</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">14691
 </t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2512
-</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">236
-</t>
-        </is>
-      </c>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="n"/>
+      <c r="R23" s="2" t="n"/>
+      <c r="S23" s="2" t="n"/>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">400
+          <t xml:space="preserve">3938
 </t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="n"/>
+          <t xml:space="preserve">23992
+</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1103
+</t>
+        </is>
+      </c>
       <c r="W23" s="2" t="n"/>
-      <c r="X23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="Y23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">691
-</t>
-        </is>
-      </c>
-      <c r="Z23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">87
-</t>
-        </is>
-      </c>
+      <c r="X23" s="2" t="n"/>
+      <c r="Y23" s="2" t="n"/>
+      <c r="Z23" s="2" t="n"/>
       <c r="AA23" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3363,116 +3162,135 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">586
+          <t xml:space="preserve">23097
 </t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t xml:space="preserve">247
+</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8510</t>
+          <t xml:space="preserve">1174
+</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">2181
 </t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr"/>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t xml:space="preserve">86
+</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>96</t>
+          <t xml:space="preserve">1188
+</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
+          <t>485</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="n"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">491
-</t>
+          <t>940</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t xml:space="preserve">121
+</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>107</t>
+          <t xml:space="preserve">1200
+</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>752</t>
+          <t xml:space="preserve">221
+</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">937
+          <t xml:space="preserve">825
 </t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>371</t>
+          <t xml:space="preserve">47
+</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">281
+</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="n"/>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7130
+</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">163
 </t>
         </is>
       </c>
-      <c r="W24" s="2" t="n"/>
-      <c r="X24" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y24" s="2" t="n"/>
-      <c r="Z24" s="2" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3485,140 +3303,137 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">397
-</t>
-        </is>
-      </c>
+      <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1791
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1448</t>
+          <t xml:space="preserve">203
+</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t xml:space="preserve">895
+</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
+          <t xml:space="preserve">1167
 </t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
+          <t xml:space="preserve">1888
 </t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">381
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2391
+          <t xml:space="preserve">1227
 </t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="n"/>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">839
 </t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">1206
 </t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
-      <c r="Y25" s="2" t="n"/>
+          <t xml:space="preserve">224
+</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1920
+</t>
+        </is>
+      </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -3636,118 +3451,119 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2798
+          <t xml:space="preserve">3700
 </t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>948</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="n"/>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="n"/>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1160
+</t>
+        </is>
+      </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr"/>
-      <c r="K26" s="2" t="n"/>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">395
+</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>1681</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1611
+</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="n"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">1930
 </t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">865
-</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr"/>
+          <t xml:space="preserve">255
+</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="n"/>
+      <c r="S26" s="2" t="n"/>
+      <c r="T26" s="2" t="n"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18020
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="n"/>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">2141
 </t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">836
 </t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -3765,145 +3581,119 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3414
+          <t xml:space="preserve">14536
 </t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">792
-67
-</t>
+          <t>518</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-1119
+          <t xml:space="preserve">1128
 </t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
+          <t xml:space="preserve">53
 </t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">970
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1150
+</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="n"/>
+      <c r="O27" s="2" t="n"/>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>411</t>
+          <t xml:space="preserve">12068
+</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">839
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1878
+</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="n"/>
+      <c r="T27" s="2" t="n"/>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
+          <t xml:space="preserve">062
 </t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="n"/>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">785
 </t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
@@ -3921,101 +3711,111 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700
+          <t xml:space="preserve">23436
 </t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="n"/>
-      <c r="F28" s="2" t="n"/>
+          <t xml:space="preserve">1263
+</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11160
+</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="n"/>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1140
+</t>
+        </is>
+      </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="n"/>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">930
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">814
+</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="n"/>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">12920
 </t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2181
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">897
-</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">696
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">238116
+</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="n"/>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">1208
 </t>
         </is>
       </c>
@@ -4027,19 +3827,19 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">1209
 </t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83836
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -4057,143 +3857,101 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4536
+          <t xml:space="preserve">17884
 </t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4007
-263
+          <t xml:space="preserve">1584
 </t>
         </is>
       </c>
       <c r="E29" s="2" t="n"/>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8414
-</t>
-        </is>
-      </c>
+      <c r="F29" s="2" t="n"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">500
 </t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>7023</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
+          <t xml:space="preserve">1630
 </t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
-</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">269
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">859
 </t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6041
-151
-</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">818
+</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="n"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>05840</t>
+          <t>4545</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17272
-</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">89
+</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="n"/>
+      <c r="R29" s="2" t="n"/>
+      <c r="S29" s="2" t="n"/>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">747
+          <t xml:space="preserve">3922
 </t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">9300
 </t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="X29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">818
+</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="n"/>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">752
-</t>
-        </is>
-      </c>
-      <c r="Z29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">120080
+</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="n"/>
       <c r="AA29" t="inlineStr">
         <is>
           <t>20</t>
@@ -4206,145 +3964,50 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3436
-</t>
-        </is>
-      </c>
+      <c r="C30" s="2" t="n"/>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">214
-</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">064
-</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">80101
+</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n"/>
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="2" t="n"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41
-</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">141
+</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n"/>
+      <c r="J30" s="2" t="n"/>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="2" t="n"/>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>551</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">865
-</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2280
-</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">815
-</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="W30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">101811
+</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="n"/>
+      <c r="O30" s="2" t="n"/>
+      <c r="P30" s="2" t="n"/>
+      <c r="Q30" s="2" t="n"/>
+      <c r="R30" s="2" t="n"/>
+      <c r="S30" s="2" t="n"/>
+      <c r="T30" s="2" t="n"/>
+      <c r="U30" s="2" t="n"/>
+      <c r="V30" s="2" t="n"/>
+      <c r="W30" s="2" t="n"/>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
-        </is>
-      </c>
-      <c r="Y30" s="2" t="inlineStr">
-        <is>
-          <t>881</t>
-        </is>
-      </c>
-      <c r="Z30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="n"/>
+      <c r="Z30" s="2" t="n"/>
       <c r="AA30" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -4359,135 +4022,130 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17884
+          <t xml:space="preserve">12666
 </t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">2867
 </t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">501
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">1822
 </t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 3
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">018
+</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
-</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n"/>
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45845
+          <t xml:space="preserve">7920
 </t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>61</t>
+          <t xml:space="preserve">010
+</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 48
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>018</t>
+          <t xml:space="preserve">1180
+</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">024
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">980
+</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">175
+</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">1169
 </t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>00</t>
+          <t xml:space="preserve">19406
+</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>002</t>
+          <t xml:space="preserve">12
+</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4504,137 +4162,105 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">357
-</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">264
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">14008
+</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n"/>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-77
+          <t xml:space="preserve">1217
 </t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1138
+</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">919
+</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">58
+</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="n"/>
+      <c r="M32" s="2" t="n"/>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-777
-</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">909
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="n"/>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">143
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="n"/>
+      <c r="R32" s="2" t="inlineStr"/>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">491
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">2794
 </t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="W32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
-      <c r="X32" s="2" t="inlineStr"/>
+          <t xml:space="preserve">896
+</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="n"/>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">834
+          <t xml:space="preserve">865
 </t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -4652,135 +4278,105 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2666
-</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">73
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">13502
+</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n"/>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">1170
 </t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1256
+</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">297
+</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="n"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="n"/>
+      <c r="O33" s="2" t="n"/>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1616
-</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="n"/>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">000
 </t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">748
 </t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
-        </is>
-      </c>
-      <c r="W33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="X33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">2018
+</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="n"/>
+      <c r="X33" s="2" t="n"/>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9461
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">2938
 </t>
         </is>
       </c>
@@ -4798,144 +4394,98 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4068
-</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">12688
+</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n"/>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">417
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="n"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">156
-</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7777
-262
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="n"/>
+      <c r="I34" s="2" t="n"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="n"/>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">147
-</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">290
+</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="n"/>
+      <c r="M34" s="2" t="n"/>
+      <c r="N34" s="2" t="n"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">780
-</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">43
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">800
+</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="n"/>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">860
 </t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="W34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1201
+</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="n"/>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">081
 </t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
-</t>
-        </is>
-      </c>
-      <c r="Z34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1164
+</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="n"/>
       <c r="AA34" t="inlineStr">
         <is>
           <t>23</t>
@@ -4950,138 +4500,110 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">356
-</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">13568
+</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n"/>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1160
+</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="n"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
-</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="n"/>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="n"/>
+      <c r="M35" s="2" t="n"/>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1837
-</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr"/>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1126
+</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">790
+</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="n"/>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t xml:space="preserve">267
+</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">068
 </t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2198
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">1602
 </t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">606
-</t>
-        </is>
-      </c>
-      <c r="Y35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">895
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1226
+</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="n"/>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -5097,134 +4619,100 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4688
-</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">281
-</t>
-        </is>
-      </c>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n"/>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">829
 </t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">11071
 </t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">485
 </t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">17106
 </t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">11667
 </t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">1606
 </t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="n"/>
-      <c r="N36" s="2" t="n"/>
+          <t xml:space="preserve">883
+</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8006
+          <t xml:space="preserve">182980
 </t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1208
+</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="n"/>
+      <c r="S36" s="2" t="n"/>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">760
-</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="n"/>
+          <t xml:space="preserve">208594
+</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1342
+</t>
+        </is>
+      </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="W36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="X36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="Y36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">956
-</t>
-        </is>
-      </c>
-      <c r="Z36" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t xml:space="preserve">2981
+</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="n"/>
+      <c r="X36" s="2" t="n"/>
+      <c r="Y36" s="2" t="n"/>
+      <c r="Z36" s="2" t="n"/>
       <c r="AA36" t="inlineStr">
         <is>
           <t>25</t>
@@ -5237,130 +4725,80 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">358
-</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n"/>
+      <c r="E37" s="2" t="n"/>
+      <c r="F37" s="2" t="n"/>
+      <c r="G37" s="2" t="n"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>806</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>313</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>883</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1141
+</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n"/>
+      <c r="J37" s="2" t="n"/>
+      <c r="K37" s="2" t="n"/>
+      <c r="L37" s="2" t="n"/>
+      <c r="M37" s="2" t="n"/>
+      <c r="N37" s="2" t="n"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
+          <t xml:space="preserve">7961
 </t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>9611</t>
+          <t xml:space="preserve">228
+</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">208
 </t>
         </is>
       </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
+      <c r="T37" s="2" t="n"/>
       <c r="U37" s="2" t="n"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">981
-2248
+          <t xml:space="preserve">296
 </t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
-181 1
+          <t xml:space="preserve">2061
 </t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="Z37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">897
+</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="n"/>
       <c r="AA37" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -5375,127 +4813,107 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6432
+          <t xml:space="preserve">122644
 </t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9637
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>085</t>
-        </is>
-      </c>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="n"/>
+      <c r="G38" s="2" t="n"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+          <t>925</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="n"/>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5247
-2272
-1
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1188
+</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n"/>
       <c r="N38" s="2" t="n"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>78</t>
+          <t xml:space="preserve">1850
+</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1298
+</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1282
+</t>
+        </is>
+      </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">638
-</t>
-        </is>
-      </c>
-      <c r="T38" s="2" t="inlineStr">
-        <is>
-          <t>558</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">2397
+</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="n"/>
+      <c r="U38" s="2" t="n"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14441
-346
-</t>
-        </is>
-      </c>
-      <c r="X38" s="2" t="n"/>
-      <c r="Y38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="Z38" s="2" t="n"/>
+          <t xml:space="preserve">1059
+</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="n"/>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2114
+</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -5510,127 +4928,126 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">12864
 </t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>9564</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-1 23
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">414
-</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">971
-</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="n"/>
+          <t xml:space="preserve">807
+</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="n"/>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
-</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr"/>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1877
+</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="n"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>8466</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1236
+</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">744
+</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="n"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1200
+</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">188
 </t>
         </is>
       </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Q39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="R39" s="2" t="inlineStr"/>
-      <c r="S39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1181
-</t>
-        </is>
-      </c>
-      <c r="T39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71
-</t>
-        </is>
-      </c>
-      <c r="U39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">350
-</t>
-        </is>
-      </c>
-      <c r="V39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="W39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1851
-</t>
-        </is>
-      </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="Y39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">889
-</t>
-        </is>
-      </c>
-      <c r="Z39" s="2" t="n"/>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="n"/>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>26</t>
@@ -5645,127 +5062,118 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2644
+          <t xml:space="preserve">123590
 </t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">1156
 </t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="n"/>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1138
+</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr"/>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n"/>
       <c r="N40" s="2" t="n"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2852
-</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">762
+</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="n"/>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">1258
 </t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21626
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231 1
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">721
+          <t xml:space="preserve">614
 </t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">2012
 </t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
-        </is>
-      </c>
-      <c r="Y40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">897
-</t>
-        </is>
-      </c>
-      <c r="Z40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="n"/>
+      <c r="Z40" s="2" t="n"/>
       <c r="AA40" t="inlineStr">
         <is>
           <t>27</t>
@@ -5780,100 +5188,72 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2864
+          <t xml:space="preserve">14866
 </t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">297
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">283
+</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n"/>
+      <c r="F41" s="2" t="n"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t xml:space="preserve">119
+</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-111
-</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1146
+</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">63
 </t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">090
-</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr"/>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1177
+</t>
+        </is>
+      </c>
       <c r="M41" s="2" t="n"/>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">766
-</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
+      <c r="N41" s="2" t="n"/>
+      <c r="O41" s="2" t="n"/>
+      <c r="P41" s="2" t="n"/>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1951
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>7444</t>
-        </is>
-      </c>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="n"/>
       <c r="U41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">168
@@ -5888,28 +5268,18 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">705
-</t>
-        </is>
-      </c>
-      <c r="Y41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="Z41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="n"/>
+      <c r="Z41" s="2" t="n"/>
       <c r="AA41" t="inlineStr">
         <is>
           <t>28</t>
@@ -5924,100 +5294,89 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3590
+          <t xml:space="preserve">19426
 </t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">156
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">276
+</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n"/>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2135
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="n"/>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">1928
 </t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-2
-</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="n"/>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1180
+</t>
+        </is>
+      </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9271249
-157
-</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1801
+</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="n"/>
+      <c r="O42" s="2" t="n"/>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">2781
 </t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">579
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -6030,28 +5389,23 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9134
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="Z42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">721
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">71
+</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="n"/>
       <c r="AA42" t="inlineStr">
         <is>
           <t>29</t>
@@ -6064,136 +5418,93 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">276
-</t>
-        </is>
-      </c>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="n"/>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>77</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="n"/>
+          <t xml:space="preserve">525
+</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1697
+</t>
+        </is>
+      </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">2681
 </t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">908
 </t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">711797
-127
-</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">99
-118
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">796
+</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="n"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">798
+          <t xml:space="preserve">12055
 </t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2031
-</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">555
-</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216868
-</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="n"/>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1195
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="n"/>
+      <c r="R43" s="2" t="n"/>
+      <c r="S43" s="2" t="n"/>
+      <c r="T43" s="2" t="n"/>
+      <c r="U43" s="2" t="n"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1048
+</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="n"/>
       <c r="X43" s="2" t="n"/>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
-        </is>
-      </c>
-      <c r="Z43" s="2" t="inlineStr">
-        <is>
-          <t>577</t>
-        </is>
-      </c>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="n"/>
       <c r="AA43" t="inlineStr">
         <is>
           <t>30</t>
@@ -6206,126 +5517,29 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-60292929572
-</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">773
-</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1577
-</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">55
-</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">697
-</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1642
-24749414
-</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">77
-</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1878
-</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42
-</t>
-        </is>
-      </c>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n"/>
+      <c r="E44" s="2" t="n"/>
+      <c r="F44" s="2" t="n"/>
+      <c r="G44" s="2" t="n"/>
+      <c r="H44" s="2" t="n"/>
+      <c r="I44" s="2" t="n"/>
+      <c r="J44" s="2" t="n"/>
+      <c r="K44" s="2" t="n"/>
+      <c r="L44" s="2" t="n"/>
+      <c r="M44" s="2" t="n"/>
       <c r="N44" s="2" t="n"/>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">727
-</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr"/>
-      <c r="Q44" s="2" t="inlineStr"/>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71
-</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">728
-</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7773
-</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">028
-</t>
-        </is>
-      </c>
+      <c r="O44" s="2" t="n"/>
+      <c r="P44" s="2" t="n"/>
+      <c r="Q44" s="2" t="n"/>
+      <c r="R44" s="2" t="n"/>
+      <c r="S44" s="2" t="n"/>
+      <c r="T44" s="2" t="n"/>
+      <c r="U44" s="2" t="n"/>
       <c r="V44" s="2" t="n"/>
-      <c r="W44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">985
-</t>
-        </is>
-      </c>
-      <c r="X44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
-      <c r="Y44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">47
-</t>
-        </is>
-      </c>
+      <c r="W44" s="2" t="n"/>
+      <c r="X44" s="2" t="n"/>
+      <c r="Y44" s="2" t="n"/>
       <c r="Z44" s="2" t="n"/>
       <c r="AA44" t="inlineStr">
         <is>
@@ -6341,76 +5555,55 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t xml:space="preserve">23689
+</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">397
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">809
+</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>946</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="n"/>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">95
+</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="n"/>
+      <c r="L45" s="2" t="n"/>
+      <c r="M45" s="2" t="n"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">164
 </t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1791287
-</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">261
-</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">79
-</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4
-1
-</t>
-        </is>
-      </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">811
@@ -6419,64 +5612,29 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t xml:space="preserve">299
+</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2628
-</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="T45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6
-</t>
-        </is>
-      </c>
-      <c r="U45" s="2" t="inlineStr">
-        <is>
-          <t>4638</t>
-        </is>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4224574
-1
-</t>
-        </is>
-      </c>
-      <c r="W45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="X45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-1
-</t>
-        </is>
-      </c>
-      <c r="Y45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">802
+</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="n"/>
+      <c r="T45" s="2" t="n"/>
+      <c r="U45" s="2" t="n"/>
+      <c r="V45" s="2" t="n"/>
+      <c r="W45" s="2" t="n"/>
+      <c r="X45" s="2" t="n"/>
+      <c r="Y45" s="2" t="n"/>
       <c r="Z45" s="2" t="n"/>
       <c r="AA45" t="inlineStr">
         <is>
@@ -6490,117 +5648,49 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">269
-</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1817857
-1 1
-1
-3
-6
-</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n"/>
+      <c r="E46" s="2" t="n"/>
+      <c r="F46" s="2" t="n"/>
+      <c r="G46" s="2" t="n"/>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">526
-</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
+          <t xml:space="preserve">44
+</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n"/>
+      <c r="J46" s="2" t="n"/>
+      <c r="K46" s="2" t="n"/>
+      <c r="L46" s="2" t="n"/>
+      <c r="M46" s="2" t="n"/>
+      <c r="N46" s="2" t="n"/>
+      <c r="O46" s="2" t="n"/>
+      <c r="P46" s="2" t="n"/>
+      <c r="Q46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">16
 </t>
         </is>
       </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr"/>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="n"/>
-      <c r="S46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">285
+</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="n"/>
       <c r="T46" s="2" t="n"/>
-      <c r="U46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1189
-</t>
-        </is>
-      </c>
-      <c r="W46" s="2" t="n"/>
+      <c r="U46" s="2" t="n"/>
+      <c r="V46" s="2" t="n"/>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8110
+</t>
+        </is>
+      </c>
       <c r="X46" s="2" t="n"/>
-      <c r="Y46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1145
-</t>
-        </is>
-      </c>
+      <c r="Y46" s="2" t="n"/>
       <c r="Z46" s="2" t="n"/>
       <c r="AA46" t="inlineStr">
         <is>
@@ -6612,62 +5702,6 @@
       <c r="B47" t="inlineStr">
         <is>
           <t>Tot.</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">324 7
-</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">727
-</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6 9
-1
-1191
-</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">

--- a/results/05_transient_transcription_output/905/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/905/Top_Excel_with_OCR_Results.xlsx
@@ -626,13 +626,13 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23898
+          <t xml:space="preserve">3898
 </t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1283
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
@@ -644,21 +644,28 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1221
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">125
+</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="n"/>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">55
@@ -667,24 +674,26 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">279
+</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0168
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t xml:space="preserve">1885
+</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -695,7 +704,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -707,11 +716,16 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="n"/>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">250
+</t>
+        </is>
+      </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">851
@@ -726,7 +740,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28208
+          <t xml:space="preserve">8203
 </t>
         </is>
       </c>
@@ -742,18 +756,8 @@
 </t>
         </is>
       </c>
-      <c r="Y4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2861
-</t>
-        </is>
-      </c>
-      <c r="Z4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
-      </c>
+      <c r="Y4" s="2" t="n"/>
+      <c r="Z4" s="2" t="n"/>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1</t>
@@ -768,13 +772,13 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14286
+          <t xml:space="preserve">4386
 </t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -786,23 +790,28 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">2060
 </t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
-</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="n"/>
+          <t xml:space="preserve">2214 4
+</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">35
@@ -811,14 +820,19 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
-</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="n"/>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">876
 </t>
         </is>
       </c>
@@ -830,42 +844,43 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1931
+          <t xml:space="preserve">931
 </t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1694
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12248
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">013
+          <t xml:space="preserve">1213
 </t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111012
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>131</t>
+          <t xml:space="preserve">843
+</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">811
 </t>
         </is>
       </c>
@@ -877,7 +892,8 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">172
+</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
@@ -892,12 +908,7 @@
 </t>
         </is>
       </c>
-      <c r="Z5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
+      <c r="Z5" s="2" t="n"/>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2</t>
@@ -919,19 +930,19 @@
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1270
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8261
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1269
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
@@ -943,32 +954,37 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">098
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="n"/>
+          <t xml:space="preserve">008
+</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">1651
 </t>
         </is>
       </c>
@@ -978,7 +994,12 @@
 </t>
         </is>
       </c>
-      <c r="P6" s="2" t="n"/>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">268
@@ -987,7 +1008,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2203
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -999,7 +1020,8 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t xml:space="preserve">690
+</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1016,13 +1038,13 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -1034,7 +1056,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -1050,10 +1072,15 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n"/>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2744
+</t>
+        </is>
+      </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">2542
 </t>
         </is>
       </c>
@@ -1065,14 +1092,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0202
-</t>
+          <t>615</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1087,28 +1112,28 @@
 </t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
+      <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">02
 </t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1279
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1698
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -1124,21 +1149,36 @@
 </t>
         </is>
       </c>
-      <c r="Q7" s="2" t="n"/>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1882
+</t>
+        </is>
+      </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">227
 </t>
         </is>
       </c>
-      <c r="S7" s="2" t="n"/>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">688
-</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr"/>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1208
@@ -1147,7 +1187,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -1165,7 +1205,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -1181,7 +1221,12 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n"/>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12602
+</t>
+        </is>
+      </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">284
@@ -1196,13 +1241,13 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">2271
 </t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
@@ -1220,13 +1265,13 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
@@ -1244,7 +1289,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1082
+          <t xml:space="preserve">1692
 </t>
         </is>
       </c>
@@ -1256,21 +1301,31 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1212
-</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="n"/>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">245
+</t>
+        </is>
+      </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">228
 </t>
         </is>
       </c>
-      <c r="S8" s="2" t="n"/>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">871
 </t>
         </is>
       </c>
@@ -1282,7 +1337,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1096
+          <t xml:space="preserve">1296
 </t>
         </is>
       </c>
@@ -1322,30 +1377,51 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="2" t="n"/>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1404
+</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">820
+</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8291
+</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1124
+</t>
+        </is>
+      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2598
+          <t xml:space="preserve">391
 </t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7221</t>
+          <t xml:space="preserve">617
+</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">2218
 </t>
         </is>
       </c>
@@ -1357,7 +1433,8 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>310</t>
+          <t xml:space="preserve">818
+</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1366,21 +1443,42 @@
 </t>
         </is>
       </c>
-      <c r="N9" s="2" t="n"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2123
+</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">342201
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="n"/>
-      <c r="R9" s="2" t="n"/>
-      <c r="S9" s="2" t="n"/>
+          <t xml:space="preserve">94
+</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1271
+</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1109
+</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4124
+</t>
+        </is>
+      </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">3842
@@ -1389,21 +1487,31 @@
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19385
-</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="n"/>
+          <t xml:space="preserve">0285
+</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9289
+</t>
+        </is>
+      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9271031
-</t>
-        </is>
-      </c>
-      <c r="X9" s="2" t="n"/>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11201
+</t>
+        </is>
+      </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194451
+          <t xml:space="preserve">94451
 </t>
         </is>
       </c>
@@ -1431,71 +1539,135 @@
 </t>
         </is>
       </c>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="n"/>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">825
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">111 8
 </t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="n"/>
-      <c r="J10" s="2" t="n"/>
-      <c r="K10" s="2" t="n"/>
+          <t xml:space="preserve">1195
+</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">821
+</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>466</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11411
+</t>
+        </is>
+      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8220171
-</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="n"/>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28211
+</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9061
-</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="n"/>
+          <t xml:space="preserve">906
+</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">289
+</t>
+        </is>
+      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="n"/>
-      <c r="S10" s="2" t="n"/>
-      <c r="T10" s="2" t="n"/>
+          <t xml:space="preserve">1254
+</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">628
+</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2124
+</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">768
+</t>
+        </is>
+      </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">77
 </t>
         </is>
       </c>
-      <c r="V10" s="2" t="n"/>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">898
+</t>
+        </is>
+      </c>
       <c r="W10" s="2" t="n"/>
-      <c r="X10" s="2" t="n"/>
-      <c r="Y10" s="2" t="n"/>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">890
+</t>
+        </is>
+      </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">2151
 </t>
         </is>
       </c>
@@ -1513,13 +1685,13 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12996
+          <t xml:space="preserve">2996
 </t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1265
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
@@ -1531,7 +1703,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
@@ -1543,67 +1715,73 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240
+          <t xml:space="preserve">1241
 </t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1014
 </t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2217
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4168</t>
+          <t xml:space="preserve">1192
+</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1270
+          <t xml:space="preserve">1810
 </t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
-</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="n"/>
+          <t xml:space="preserve">281
+</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">064
 </t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2660
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2290
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
@@ -1615,27 +1793,37 @@
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">1106
 </t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="X11" s="2" t="n"/>
-      <c r="Y11" s="2" t="n"/>
+          <t xml:space="preserve">1198
+</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">845
+</t>
+        </is>
+      </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -1653,7 +1841,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23436
+          <t xml:space="preserve">03436
 </t>
         </is>
       </c>
@@ -1665,19 +1853,19 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">878
 </t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -1695,13 +1883,13 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1284
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -1719,24 +1907,25 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1036
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1921
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">166
+</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -1748,12 +1937,13 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1930
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
@@ -1765,26 +1955,31 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
-</t>
-        </is>
-      </c>
-      <c r="Y12" s="2" t="n"/>
+          <t xml:space="preserve">2129
+</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">891
+</t>
+        </is>
+      </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -1802,7 +1997,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23238
+          <t xml:space="preserve">293238
 </t>
         </is>
       </c>
@@ -1824,24 +2019,35 @@
 </t>
         </is>
       </c>
-      <c r="G13" s="2" t="n"/>
-      <c r="H13" s="2" t="n"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="n"/>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">877
+</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1852,7 +2058,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
@@ -1862,15 +2068,10 @@
 </t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1815
-</t>
-        </is>
-      </c>
+      <c r="P13" s="2" t="inlineStr"/>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2164
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
@@ -1888,7 +2089,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
@@ -1906,7 +2107,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1994
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
@@ -1918,13 +2119,13 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">958
 </t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
@@ -1942,8 +2143,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2600
-</t>
+          <t>86004</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1954,17 +2154,28 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>484</t>
+          <t xml:space="preserve">174
+</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="n"/>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">914
+</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">126
@@ -1973,26 +2184,31 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2212
-</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="n"/>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1183
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -2004,13 +2220,13 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -2028,13 +2244,13 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1958
+          <t xml:space="preserve">956
 </t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -2052,14 +2268,19 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="Y14" s="2" t="n"/>
+          <t xml:space="preserve">225
+</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
@@ -2077,7 +2298,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23348
+          <t xml:space="preserve">9348
 </t>
         </is>
       </c>
@@ -2095,39 +2316,49 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">029
 </t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1017
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
-</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr"/>
+          <t xml:space="preserve">814
+</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10914
-</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="n"/>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">246
+</t>
+        </is>
+      </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
@@ -2145,19 +2376,19 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2214
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
@@ -2169,26 +2400,31 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1993
+          <t xml:space="preserve">9953
 </t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="n"/>
+          <t xml:space="preserve">1192
+</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1060
+          <t xml:space="preserve">2023
 </t>
         </is>
       </c>
@@ -2200,7 +2436,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -2218,13 +2454,13 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101618
+          <t xml:space="preserve">02688
 </t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1348
+          <t xml:space="preserve">14281
 </t>
         </is>
       </c>
@@ -2242,13 +2478,13 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14814
+          <t xml:space="preserve">4814
 </t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">720
+          <t xml:space="preserve">1908
 </t>
         </is>
       </c>
@@ -2260,13 +2496,13 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118126
+          <t xml:space="preserve">981
 </t>
         </is>
       </c>
@@ -2276,40 +2512,63 @@
 </t>
         </is>
       </c>
-      <c r="M16" s="2" t="n"/>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">853
+</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">956
 </t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86531</t>
+          <t xml:space="preserve">14659
+</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>619</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="n"/>
-      <c r="R16" s="2" t="n"/>
-      <c r="S16" s="2" t="n"/>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0169
+</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3114
+</t>
+        </is>
+      </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4196</t>
+          <t xml:space="preserve">99208
+</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133591
+          <t xml:space="preserve">358
 </t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11018
+          <t xml:space="preserve">1018
 </t>
         </is>
       </c>
@@ -2321,13 +2580,13 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1097
+          <t xml:space="preserve">1087
 </t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4574
+          <t xml:space="preserve">46584
 </t>
         </is>
       </c>
@@ -2349,54 +2608,114 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n"/>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3124
+</t>
+        </is>
+      </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">8816
 </t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19113
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8171
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">120117
+</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="n"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">146
 </t>
         </is>
       </c>
-      <c r="I17" s="2" t="n"/>
-      <c r="J17" s="2" t="n"/>
-      <c r="K17" s="2" t="n"/>
-      <c r="L17" s="2" t="n"/>
-      <c r="M17" s="2" t="n"/>
-      <c r="N17" s="2" t="n"/>
-      <c r="O17" s="2" t="n"/>
-      <c r="P17" s="2" t="n"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1178
+</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1190
+</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">932
+</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1111
+</t>
+        </is>
+      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">239
 </t>
         </is>
       </c>
-      <c r="R17" s="2" t="n"/>
-      <c r="S17" s="2" t="n"/>
-      <c r="T17" s="2" t="n"/>
-      <c r="U17" s="2" t="n"/>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2691
+</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2298
+</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7884
+</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70
+</t>
+        </is>
+      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">204
@@ -2405,13 +2724,28 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="X17" s="2" t="n"/>
-      <c r="Y17" s="2" t="n"/>
-      <c r="Z17" s="2" t="n"/>
+          <t xml:space="preserve">294
+</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">915
+</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2426,19 +2760,20 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9546
+          <t xml:space="preserve">29546
 </t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">2771
 </t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>180</t>
+          <t xml:space="preserve">170
+</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2455,79 +2790,109 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
-</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="n"/>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1130
+</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">55
+</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1082
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">2868
 </t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">1883
 </t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
+          <t xml:space="preserve">871
 </t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">267
+</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1228
+</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">141487
+</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">1267
 </t>
         </is>
       </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2128
-</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1239
-</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="n"/>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1247
-</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1069
-</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="n"/>
-      <c r="X18" s="2" t="n"/>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">835
+          <t xml:space="preserve">800
 </t>
         </is>
       </c>
@@ -2549,7 +2914,12 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="2" t="n"/>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1194
+</t>
+        </is>
+      </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">274
@@ -2564,22 +2934,37 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">8288
 </t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="n"/>
-      <c r="J19" s="2" t="n"/>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
@@ -2591,13 +2976,13 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">1874
 </t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">089
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
@@ -2609,7 +2994,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1218
 </t>
         </is>
       </c>
@@ -2627,23 +3012,34 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="n"/>
+          <t xml:space="preserve">2080
+</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">131
+</t>
+        </is>
+      </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="n"/>
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">212
@@ -2652,13 +3048,13 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">736
 </t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
@@ -2674,7 +3070,12 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n"/>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">534
+</t>
+        </is>
+      </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">268
@@ -2683,28 +3084,49 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="n"/>
-      <c r="H20" s="2" t="n"/>
-      <c r="I20" s="2" t="n"/>
-      <c r="J20" s="2" t="n"/>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91
+</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0219
+</t>
+        </is>
+      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -2716,14 +3138,19 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="n"/>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -2745,10 +3172,14 @@
 </t>
         </is>
       </c>
-      <c r="T20" s="2" t="n"/>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1231
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
@@ -2758,10 +3189,15 @@
 </t>
         </is>
       </c>
-      <c r="W20" s="2" t="n"/>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
@@ -2773,7 +3209,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -2791,19 +3227,20 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12848
+          <t xml:space="preserve">18246
 </t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">2018
 </t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t xml:space="preserve">170
+</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2812,24 +3249,39 @@
 </t>
         </is>
       </c>
-      <c r="G21" s="2" t="n"/>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1711
+</t>
+        </is>
+      </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="n"/>
-      <c r="J21" s="2" t="n"/>
+          <t xml:space="preserve">870
+</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">282
+</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">1680
 </t>
         </is>
       </c>
@@ -2839,8 +3291,18 @@
 </t>
         </is>
       </c>
-      <c r="N21" s="2" t="n"/>
-      <c r="O21" s="2" t="n"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1289
+</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">940
+</t>
+        </is>
+      </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">182
@@ -2861,26 +3323,31 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
-</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="n"/>
+          <t xml:space="preserve">286
+</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">911
+</t>
+        </is>
+      </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2262
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0206
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -2892,12 +3359,13 @@
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>961</t>
+          <t xml:space="preserve">968
+</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -2915,7 +3383,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23392
+          <t xml:space="preserve">3392
 </t>
         </is>
       </c>
@@ -2939,47 +3407,52 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">106 2
 </t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">846
 </t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1171
-</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="n"/>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">980
@@ -2988,13 +3461,14 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t xml:space="preserve">251
+</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
@@ -3011,7 +3485,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
@@ -3023,13 +3497,13 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">12190
 </t>
         </is>
       </c>
@@ -3047,7 +3521,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
@@ -3063,36 +3537,57 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n"/>
-      <c r="E23" s="2" t="n"/>
-      <c r="F23" s="2" t="n"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">850
+</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t xml:space="preserve">926
+</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">748
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11212
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1699
+          <t xml:space="preserve">1299
 </t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t xml:space="preserve">66
+</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -3103,51 +3598,83 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8894</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">818
+</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14691
+          <t xml:space="preserve">2691
 </t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="n"/>
-      <c r="R23" s="2" t="n"/>
-      <c r="S23" s="2" t="n"/>
+          <t xml:space="preserve">620
+</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81158
+</t>
+        </is>
+      </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3938
+          <t xml:space="preserve">2991
 </t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23992
+          <t xml:space="preserve">992
 </t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
-</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="n"/>
-      <c r="X23" s="2" t="n"/>
-      <c r="Y23" s="2" t="n"/>
-      <c r="Z23" s="2" t="n"/>
+          <t xml:space="preserve">1100
+</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1996
+</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2100
+</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4068
+</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1229
+</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3168,126 +3695,129 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">1701
 </t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2181
+          <t xml:space="preserve">2221
 </t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">18 051
+</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">2541
 </t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">291
+</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>485</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="n"/>
+          <t xml:space="preserve">1741
+</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t xml:space="preserve">9381
+</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">2391
 </t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
+          <t xml:space="preserve">2101
 </t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2321
+</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">221
 </t>
         </is>
       </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">825
-</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">47
-</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">281
-</t>
-        </is>
-      </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="X24" s="2" t="n"/>
-      <c r="Y24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7130
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">299
+</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211834
+</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="n"/>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
@@ -3303,101 +3833,110 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2798
+</t>
+        </is>
+      </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">895
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">004
 </t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1167
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1888
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">940
 </t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1227
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="n"/>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
+          <t xml:space="preserve">825
 </t>
         </is>
       </c>
@@ -3409,31 +3948,31 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1920
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">63
 </t>
         </is>
       </c>
@@ -3451,119 +3990,145 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700
+          <t xml:space="preserve">3414
 </t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">203
+</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91
+</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8253
+</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37
+</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1170
+</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">167
 </t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1160
-</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">395
-</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>1681</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1611
-</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="n"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1828
+</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1930
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="n"/>
-      <c r="S26" s="2" t="n"/>
-      <c r="T26" s="2" t="n"/>
+          <t xml:space="preserve">227
+</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2416
+</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">246
+</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">839
+</t>
+        </is>
+      </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="n"/>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">197
+</t>
+        </is>
+      </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2141
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">836
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -3581,119 +4146,142 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14536
+          <t xml:space="preserve">3700
 </t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>461</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>464</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">251
+</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">930
+</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">255
+</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">219
 </t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1128
-</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">53
-</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1150
-</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="n"/>
-      <c r="O27" s="2" t="n"/>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12068
-</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1878
-</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="n"/>
-      <c r="T27" s="2" t="n"/>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">287
+</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>6364</t>
+        </is>
+      </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">062
+          <t xml:space="preserve">909
 </t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="n"/>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">785
+          <t xml:space="preserve">836
 </t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -3711,135 +4299,143 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23436
+          <t xml:space="preserve">4536
 </t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1263
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11160
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
+          <t xml:space="preserve">1128
 </t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">933
 </t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
-</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="n"/>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">840
+</t>
+        </is>
+      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12920
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238116
-</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="n"/>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1209
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">785
 </t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -3857,101 +4453,138 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17884
+          <t xml:space="preserve">3436
 </t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1584
-</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="n"/>
-      <c r="F29" s="2" t="n"/>
+          <t xml:space="preserve">1265
+</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1162
+</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7023</t>
+          <t xml:space="preserve">140
+</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1630
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr"/>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">619
+</t>
+        </is>
+      </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="n"/>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>4545</t>
-        </is>
-      </c>
+          <t xml:space="preserve">155
+</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr"/>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="n"/>
-      <c r="R29" s="2" t="n"/>
-      <c r="S29" s="2" t="n"/>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">197
+</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">816
+</t>
+        </is>
+      </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3922
+          <t xml:space="preserve">815
 </t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9300
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
-        </is>
-      </c>
-      <c r="X29" s="2" t="n"/>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120080
-</t>
-        </is>
-      </c>
-      <c r="Z29" s="2" t="n"/>
+          <t xml:space="preserve">880
+</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>20</t>
@@ -3964,50 +4597,145 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1869
+</t>
+        </is>
+      </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80101
-</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="n"/>
-      <c r="F30" s="2" t="n"/>
-      <c r="G30" s="2" t="n"/>
+          <t xml:space="preserve">244
+</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">817
+</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1004
+</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="n"/>
-      <c r="J30" s="2" t="n"/>
-      <c r="K30" s="2" t="n"/>
-      <c r="L30" s="2" t="n"/>
+          <t xml:space="preserve">7009
+</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1200
+</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1190
+</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8939
+</t>
+        </is>
+      </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101811
-</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="n"/>
-      <c r="O30" s="2" t="n"/>
-      <c r="P30" s="2" t="n"/>
-      <c r="Q30" s="2" t="n"/>
+          <t xml:space="preserve">812
+</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8 10
+</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14249
+</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">89
+</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1112
+</t>
+        </is>
+      </c>
       <c r="R30" s="2" t="n"/>
-      <c r="S30" s="2" t="n"/>
-      <c r="T30" s="2" t="n"/>
-      <c r="U30" s="2" t="n"/>
-      <c r="V30" s="2" t="n"/>
-      <c r="W30" s="2" t="n"/>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81094
+</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2222
+</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">909
+</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1118
+</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">918
+</t>
+        </is>
+      </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="Y30" s="2" t="n"/>
-      <c r="Z30" s="2" t="n"/>
+          <t xml:space="preserve">9998
+</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1161
+</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1200
+</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -4022,129 +4750,140 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12666
+          <t xml:space="preserve">23577
 </t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t xml:space="preserve">12862
+</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">1163
 </t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2867
+          <t xml:space="preserve">1215
 </t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">111001
 </t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1822
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">018
-</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="n"/>
+          <t xml:space="preserve">9 9
+</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="n"/>
-      <c r="N31" s="2" t="inlineStr"/>
+          <t xml:space="preserve">11721
+</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101208101
+</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="n"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7920
+          <t xml:space="preserve">909
 </t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">010
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">12 66
 </t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">2191
 </t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">784
 </t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">611
 </t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">1841
 </t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19406
+          <t xml:space="preserve">832
 </t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">401
 </t>
         </is>
       </c>
@@ -4162,105 +4901,145 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14008
-</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="n"/>
+          <t xml:space="preserve">2666
+</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">1291
 </t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">816
 </t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="n"/>
+          <t xml:space="preserve">1894
+</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1856
+</t>
+        </is>
+      </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
+          <t xml:space="preserve">2014
 </t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="n"/>
-      <c r="M32" s="2" t="n"/>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="n"/>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="n"/>
-      <c r="R32" s="2" t="inlineStr"/>
+          <t xml:space="preserve">010
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1189
+</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1180
+</t>
+        </is>
+      </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">12064
 </t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2794
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">896
-</t>
-        </is>
-      </c>
-      <c r="W32" s="2" t="n"/>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1162
+</t>
+        </is>
+      </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">0081
 </t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">865
+          <t xml:space="preserve">940
 </t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">1820
 </t>
         </is>
       </c>
@@ -4278,105 +5057,145 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13502
-</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="n"/>
+          <t xml:space="preserve">14008
+</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">273
+</t>
+        </is>
+      </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">1217
 </t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">1111
 </t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1256
-</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="n"/>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="n"/>
+          <t xml:space="preserve">58
+</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">171
+</t>
+        </is>
+      </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="n"/>
-      <c r="O33" s="2" t="n"/>
+          <t xml:space="preserve">018
+</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">811
+</t>
+        </is>
+      </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="n"/>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2184
+</t>
+        </is>
+      </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">000
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">748
+          <t xml:space="preserve">774
 </t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018
-</t>
-        </is>
-      </c>
-      <c r="W33" s="2" t="n"/>
-      <c r="X33" s="2" t="n"/>
+          <t xml:space="preserve">1896
+</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1880
+</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">868
 </t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2938
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
@@ -4394,98 +5213,147 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12688
-</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="n"/>
+          <t xml:space="preserve">23502
+</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="n"/>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="n"/>
-      <c r="I34" s="2" t="n"/>
+          <t xml:space="preserve">79
+</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1156
+</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="n"/>
-      <c r="M34" s="2" t="n"/>
-      <c r="N34" s="2" t="n"/>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1166
+</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1119
+</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
-</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="n"/>
+          <t xml:space="preserve">918
+</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
+          <t xml:space="preserve">748
 </t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1201
-</t>
-        </is>
-      </c>
-      <c r="W34" s="2" t="n"/>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">081
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
-</t>
-        </is>
-      </c>
-      <c r="Z34" s="2" t="n"/>
+          <t xml:space="preserve">840
+</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>23</t>
@@ -4500,67 +5368,95 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13568
-</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="n"/>
+          <t xml:space="preserve">2688
+</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
-</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="n"/>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="n"/>
+          <t xml:space="preserve">89
+</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800
+</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">40
 </t>
         </is>
       </c>
-      <c r="L35" s="2" t="n"/>
-      <c r="M35" s="2" t="n"/>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1126
-</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">790
-</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="n"/>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">068
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -4572,38 +5468,43 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1602
+          <t xml:space="preserve">860
 </t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
-</t>
-        </is>
-      </c>
-      <c r="Y35" s="2" t="n"/>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">892
+</t>
+        </is>
+      </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">2441
 </t>
         </is>
       </c>
@@ -4619,100 +5520,145 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3568
+</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">281
+</t>
+        </is>
+      </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11071
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">485
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17106
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11667
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1606
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">883
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182980
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
-</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr"/>
-      <c r="R36" s="2" t="n"/>
-      <c r="S36" s="2" t="n"/>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">267
+</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208594
+          <t xml:space="preserve">602
 </t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1342
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2981
-</t>
-        </is>
-      </c>
-      <c r="W36" s="2" t="n"/>
-      <c r="X36" s="2" t="n"/>
-      <c r="Y36" s="2" t="n"/>
-      <c r="Z36" s="2" t="n"/>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">952
+</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>25</t>
@@ -4725,76 +5671,135 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="n"/>
-      <c r="E37" s="2" t="n"/>
-      <c r="F37" s="2" t="n"/>
-      <c r="G37" s="2" t="n"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16402
+</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16211
+</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13011
+</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">485
+</t>
+        </is>
+      </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141
-</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="n"/>
-      <c r="J37" s="2" t="n"/>
-      <c r="K37" s="2" t="n"/>
-      <c r="L37" s="2" t="n"/>
-      <c r="M37" s="2" t="n"/>
-      <c r="N37" s="2" t="n"/>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1067
+</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16006
+</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">880
+</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">860
+</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7961
+          <t xml:space="preserve">2980
 </t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">1808
 </t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">1229
 </t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">1461
 </t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="n"/>
-      <c r="U37" s="2" t="n"/>
+          <t xml:space="preserve">1008
+</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1942
+</t>
+        </is>
+      </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
+          <t xml:space="preserve">981
 </t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="X37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2061
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">9212
+</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="n"/>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">897
+          <t xml:space="preserve">44817
 </t>
         </is>
       </c>
@@ -4811,109 +5816,135 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122644
-</t>
-        </is>
-      </c>
+      <c r="C38" s="2" t="n"/>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">2631
 </t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="n"/>
-      <c r="G38" s="2" t="n"/>
+          <t xml:space="preserve">8661
+</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">971
+</t>
+        </is>
+      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">1141
 </t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="n"/>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1231
+</t>
+        </is>
+      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="n"/>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="n"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1850
+          <t xml:space="preserve">7961
 </t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1298
+          <t xml:space="preserve">2122
 </t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">117 8
 </t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2397
-</t>
-        </is>
-      </c>
-      <c r="T38" s="2" t="n"/>
-      <c r="U38" s="2" t="n"/>
+          <t xml:space="preserve">1118
+</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7711
+</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1464
+</t>
+        </is>
+      </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1059
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="Y38" s="2" t="n"/>
-      <c r="Z38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2114
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">2086
+</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">891
+</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="n"/>
       <c r="AA38" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -4928,13 +5959,14 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12864
+          <t xml:space="preserve">2864
 </t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>9564</t>
+          <t xml:space="preserve">256
+</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -4945,7 +5977,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">807
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -4958,7 +5990,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -4976,25 +6008,26 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1877
+          <t xml:space="preserve">1077
 </t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="N39" s="2" t="n"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>8466</t>
+          <t xml:space="preserve">885
+</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1236
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
@@ -5004,50 +6037,15 @@
 </t>
         </is>
       </c>
-      <c r="R39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="S39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="T39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">744
-</t>
-        </is>
-      </c>
+      <c r="R39" s="2" t="n"/>
+      <c r="S39" s="2" t="n"/>
+      <c r="T39" s="2" t="n"/>
       <c r="U39" s="2" t="n"/>
-      <c r="V39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1200
-</t>
-        </is>
-      </c>
-      <c r="W39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="X39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
+      <c r="V39" s="2" t="n"/>
+      <c r="W39" s="2" t="n"/>
+      <c r="X39" s="2" t="n"/>
       <c r="Y39" s="2" t="n"/>
-      <c r="Z39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">214
-</t>
-        </is>
-      </c>
+      <c r="Z39" s="2" t="n"/>
       <c r="AA39" t="inlineStr">
         <is>
           <t>26</t>
@@ -5062,7 +6060,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123590
+          <t xml:space="preserve">53590
 </t>
         </is>
       </c>
@@ -5074,59 +6072,69 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1156
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">01116
+</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="n"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1138
 </t>
         </is>
       </c>
-      <c r="I40" s="2" t="n"/>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">859
+</t>
+        </is>
+      </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">58
+</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">180
 </t>
         </is>
       </c>
-      <c r="M40" s="2" t="n"/>
-      <c r="N40" s="2" t="n"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">762
-</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="n"/>
+          <t xml:space="preserve">862
+</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -5156,7 +6164,7 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2012
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
@@ -5168,12 +6176,22 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="Y40" s="2" t="n"/>
-      <c r="Z40" s="2" t="n"/>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">862
+</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">814
+</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>27</t>
@@ -5188,8 +6206,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14866
-</t>
+          <t>88664</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -5198,27 +6215,27 @@
 </t>
         </is>
       </c>
-      <c r="E41" s="2" t="n"/>
-      <c r="F41" s="2" t="n"/>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1146
-</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="n"/>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">63
-</t>
-        </is>
-      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="n"/>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="n"/>
       <c r="K41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -5227,14 +6244,34 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1177
-</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="n"/>
-      <c r="N41" s="2" t="n"/>
-      <c r="O41" s="2" t="n"/>
-      <c r="P41" s="2" t="n"/>
+          <t xml:space="preserve">277
+</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">820
+</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">500
+</t>
+        </is>
+      </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">260
@@ -5253,10 +6290,15 @@
 </t>
         </is>
       </c>
-      <c r="T41" s="2" t="n"/>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">579
+</t>
+        </is>
+      </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -5266,20 +6308,25 @@
 </t>
         </is>
       </c>
-      <c r="W41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
+      <c r="W41" s="2" t="inlineStr"/>
       <c r="X41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">202
 </t>
         </is>
       </c>
-      <c r="Y41" s="2" t="n"/>
-      <c r="Z41" s="2" t="n"/>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">734
+</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>28</t>
@@ -5294,7 +6341,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19426
+          <t xml:space="preserve">9426
 </t>
         </is>
       </c>
@@ -5304,10 +6351,15 @@
 </t>
         </is>
       </c>
-      <c r="E42" s="2" t="n"/>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">2019
 </t>
         </is>
       </c>
@@ -5319,46 +6371,56 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1928
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1801
-</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="n"/>
-      <c r="O42" s="2" t="n"/>
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1160
+</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">798
+</t>
+        </is>
+      </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2781
+          <t xml:space="preserve">2841
 </t>
         </is>
       </c>
@@ -5370,17 +6432,22 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">8299
 </t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="n"/>
+          <t xml:space="preserve">555
+</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">222
@@ -5395,17 +6462,22 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">897
 </t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">71
 </t>
         </is>
       </c>
-      <c r="Z42" s="2" t="n"/>
       <c r="AA42" t="inlineStr">
         <is>
           <t>29</t>
@@ -5419,50 +6491,57 @@
         </is>
       </c>
       <c r="C43" s="2" t="n"/>
-      <c r="D43" s="2" t="n"/>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">948
+</t>
+        </is>
+      </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t xml:space="preserve">8109
+</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>77</t>
+          <t xml:space="preserve">1081
+</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">525
+          <t xml:space="preserve">2211
 </t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1697
+          <t xml:space="preserve">0914
 </t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">1619
 </t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2681
+          <t xml:space="preserve">1261
 </t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">908
+          <t xml:space="preserve">902
 </t>
         </is>
       </c>
@@ -5475,32 +6554,67 @@
       <c r="N43" s="2" t="n"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12055
+          <t xml:space="preserve">1055
 </t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="n"/>
-      <c r="R43" s="2" t="n"/>
-      <c r="S43" s="2" t="n"/>
-      <c r="T43" s="2" t="n"/>
-      <c r="U43" s="2" t="n"/>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1251
+</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16 16
+</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">536
+</t>
+        </is>
+      </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1048
 </t>
         </is>
       </c>
-      <c r="W43" s="2" t="n"/>
-      <c r="X43" s="2" t="n"/>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2193
+</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201 10
+</t>
+        </is>
+      </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">4 067
 </t>
         </is>
       </c>
@@ -5517,7 +6631,12 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="2" t="n"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D44" s="2" t="n"/>
       <c r="E44" s="2" t="n"/>
       <c r="F44" s="2" t="n"/>
@@ -5555,7 +6674,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23689
+          <t xml:space="preserve">3629
 </t>
         </is>
       </c>
@@ -5567,19 +6686,25 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">809
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>946</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="n"/>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
@@ -5595,12 +6720,27 @@
 </t>
         </is>
       </c>
-      <c r="K45" s="2" t="n"/>
-      <c r="L45" s="2" t="n"/>
-      <c r="M45" s="2" t="n"/>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1180
+</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15 9
+</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -5612,29 +6752,64 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">802
-</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="n"/>
-      <c r="T45" s="2" t="n"/>
-      <c r="U45" s="2" t="n"/>
-      <c r="V45" s="2" t="n"/>
-      <c r="W45" s="2" t="n"/>
-      <c r="X45" s="2" t="n"/>
-      <c r="Y45" s="2" t="n"/>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">660
+</t>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47
+</t>
+        </is>
+      </c>
       <c r="Z45" s="2" t="n"/>
       <c r="AA45" t="inlineStr">
         <is>
@@ -5648,48 +6823,123 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n"/>
-      <c r="E46" s="2" t="n"/>
-      <c r="F46" s="2" t="n"/>
-      <c r="G46" s="2" t="n"/>
+      <c r="C46" s="2" t="inlineStr"/>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="n"/>
-      <c r="J46" s="2" t="n"/>
-      <c r="K46" s="2" t="n"/>
-      <c r="L46" s="2" t="n"/>
-      <c r="M46" s="2" t="n"/>
-      <c r="N46" s="2" t="n"/>
-      <c r="O46" s="2" t="n"/>
-      <c r="P46" s="2" t="n"/>
+          <t xml:space="preserve">014
+</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4
+</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14107
+</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">285
-</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="n"/>
-      <c r="T46" s="2" t="n"/>
-      <c r="U46" s="2" t="n"/>
-      <c r="V46" s="2" t="n"/>
+          <t xml:space="preserve">4
+</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4
+</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8110
-</t>
-        </is>
-      </c>
-      <c r="X46" s="2" t="n"/>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4
+</t>
+        </is>
+      </c>
       <c r="Y46" s="2" t="n"/>
       <c r="Z46" s="2" t="n"/>
       <c r="AA46" t="inlineStr">

--- a/results/05_transient_transcription_output/905/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/905/Top_Excel_with_OCR_Results.xlsx
@@ -632,13 +632,13 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">883
 </t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
@@ -650,16 +650,16 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">825
+</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">125
 </t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">38
@@ -674,13 +674,13 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -704,7 +704,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -722,7 +722,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">1250
 </t>
         </is>
       </c>
@@ -740,7 +740,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8203
+          <t xml:space="preserve">803
 </t>
         </is>
       </c>
@@ -772,14 +772,13 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4386
+          <t xml:space="preserve">94326
 </t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -796,13 +795,13 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2060
+          <t xml:space="preserve">02150
 </t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2214 4
+          <t xml:space="preserve">2211
 </t>
         </is>
       </c>
@@ -820,7 +819,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">1223
 </t>
         </is>
       </c>
@@ -832,7 +831,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">876
+          <t xml:space="preserve">0176
 </t>
         </is>
       </c>
@@ -844,7 +843,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">931
+          <t xml:space="preserve">981
 </t>
         </is>
       </c>
@@ -862,7 +861,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1213
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
@@ -874,7 +873,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">843
+          <t xml:space="preserve">743
 </t>
         </is>
       </c>
@@ -966,7 +965,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">008
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -978,22 +977,17 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1651
-</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">281
+</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr"/>
       <c r="P6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">16
@@ -1074,13 +1068,13 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2744
+          <t xml:space="preserve">3844
 </t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2542
+          <t xml:space="preserve">1281
 </t>
         </is>
       </c>
@@ -1092,12 +1086,14 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">120
+</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1112,7 +1108,11 @@
 </t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">02
@@ -1133,14 +1133,13 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1151,7 +1150,7 @@
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1882
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
@@ -1169,7 +1168,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">687
 </t>
         </is>
       </c>
@@ -1181,7 +1180,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -1223,7 +1222,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12602
+          <t xml:space="preserve">2602
 </t>
         </is>
       </c>
@@ -1241,7 +1240,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2271
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
@@ -1265,79 +1264,79 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">33
+</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">41
+</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1672
+</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">882
+</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">245
+</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">871
+</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">39
 </t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41
-</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1692
-</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">882
-</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">245
-</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">871
-</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1296
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -1379,37 +1378,36 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1404
-</t>
+          <t>34405</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">18248
 </t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8291
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">391
+          <t xml:space="preserve">991
 </t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">617
+          <t xml:space="preserve">618
 </t>
         </is>
       </c>
@@ -1421,19 +1419,19 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2218
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">814
 </t>
         </is>
       </c>
@@ -1445,13 +1443,13 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2123
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
@@ -1469,16 +1467,11 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
-</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4124
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">0912
+</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="n"/>
       <c r="T9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">3842
@@ -1487,13 +1480,13 @@
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0285
+          <t xml:space="preserve">385
 </t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9289
+          <t xml:space="preserve">989
 </t>
         </is>
       </c>
@@ -1505,19 +1498,19 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11201
+          <t xml:space="preserve">1628
 </t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94451
+          <t xml:space="preserve">4458
 </t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1228
 </t>
         </is>
       </c>
@@ -1541,7 +1534,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">2891
 </t>
         </is>
       </c>
@@ -1553,54 +1546,52 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111 8
-</t>
+          <t>468</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">2821
 </t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>466</t>
+          <t xml:space="preserve">146
+</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11411
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28211
+          <t xml:space="preserve">16878
 </t>
         </is>
       </c>
@@ -1612,25 +1603,25 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1254
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2124
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -1648,7 +1639,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
+          <t xml:space="preserve">1981
 </t>
         </is>
       </c>
@@ -1667,7 +1658,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2151
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -1697,62 +1688,60 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">868
 </t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>911</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1014
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
+          <t xml:space="preserve">8311
 </t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1810
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>414</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1763,7 +1752,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">064
+          <t xml:space="preserve">084
 </t>
         </is>
       </c>
@@ -1775,13 +1764,13 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">2163
 </t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
@@ -1799,7 +1788,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -1811,7 +1800,7 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
@@ -1841,7 +1830,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03436
+          <t xml:space="preserve">3436
 </t>
         </is>
       </c>
@@ -1853,13 +1842,13 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -1889,7 +1878,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
@@ -1913,19 +1902,19 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">926
 </t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -1937,13 +1926,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>086</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
+          <t xml:space="preserve">9230
 </t>
         </is>
       </c>
@@ -1967,7 +1955,7 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2129
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -1979,7 +1967,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -1997,7 +1985,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293238
+          <t xml:space="preserve">23238
 </t>
         </is>
       </c>
@@ -2009,7 +1997,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
@@ -2040,34 +2028,29 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">877
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">922
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr"/>
       <c r="P13" s="2" t="inlineStr"/>
       <c r="Q13" s="2" t="inlineStr">
         <is>
@@ -2089,7 +2072,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
@@ -2101,19 +2084,19 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">294
 </t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
@@ -2143,7 +2126,8 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>86004</t>
+          <t xml:space="preserve">2600
+</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2166,13 +2150,13 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">914
+          <t xml:space="preserve">984
 </t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
@@ -2184,7 +2168,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
@@ -2196,19 +2180,19 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">4189
 </t>
         </is>
       </c>
@@ -2220,7 +2204,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -2250,7 +2234,7 @@
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
@@ -2274,7 +2258,7 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
@@ -2298,7 +2282,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9348
+          <t xml:space="preserve">2348
 </t>
         </is>
       </c>
@@ -2316,25 +2300,25 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">029
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">18 7
 </t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
+          <t xml:space="preserve">1 44 1
 </t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -2358,7 +2342,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -2400,7 +2384,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9953
+          <t xml:space="preserve">593
 </t>
         </is>
       </c>
@@ -2412,7 +2396,7 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -2424,13 +2408,13 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -2454,13 +2438,13 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02688
+          <t xml:space="preserve">03618
 </t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14281
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
@@ -2478,13 +2462,13 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4814
+          <t xml:space="preserve">24814
 </t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1908
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -2494,40 +2478,33 @@
 </t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1149
-</t>
-        </is>
-      </c>
+      <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">981
+          <t xml:space="preserve">989
 </t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
+          <t>688</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">853
+          <t xml:space="preserve">833
 </t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">956
+          <t xml:space="preserve">950
 </t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14659
-</t>
+          <t>659</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2538,55 +2515,53 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>71603</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11 29
+</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">831
+</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1018
+</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">869
+</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">109
 </t>
         </is>
       </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0169
-</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3114
-</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">99208
-</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">358
-</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1018
-</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">969
-</t>
-        </is>
-      </c>
-      <c r="X16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1087
-</t>
-        </is>
-      </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46584
+          <t xml:space="preserve">4584
 </t>
         </is>
       </c>
@@ -2616,19 +2591,19 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8816
+          <t xml:space="preserve">1601
 </t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120117
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -2641,7 +2616,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>4816</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2652,7 +2627,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -2664,13 +2639,13 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -2682,7 +2657,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -2706,7 +2681,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7884
+          <t xml:space="preserve">1887
 </t>
         </is>
       </c>
@@ -2724,7 +2699,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">1294
 </t>
         </is>
       </c>
@@ -2736,13 +2711,13 @@
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">915
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -2760,13 +2735,13 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29546
+          <t xml:space="preserve">2546
 </t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2771
+          <t xml:space="preserve">277
 </t>
         </is>
       </c>
@@ -2776,39 +2751,32 @@
 </t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2209
-</t>
-        </is>
-      </c>
+      <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1167
+          <t xml:space="preserve">1867
 </t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>506</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -2820,25 +2788,25 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2868
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1883
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">871
+          <t xml:space="preserve">811
 </t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
@@ -2850,25 +2818,24 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>8491</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">1665
 </t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141487
+          <t xml:space="preserve">1418
 </t>
         </is>
       </c>
@@ -2886,19 +2853,19 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1267
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
@@ -2916,7 +2883,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
@@ -2934,118 +2901,118 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8288
+          <t xml:space="preserve">2088
 </t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33
+</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">274
+</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">135
+</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">940
+</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8881
+</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">131
+</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">89
+</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">212
 </t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">253
-</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1874
-</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">940
-</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1218
-</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2080
-</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">131
-</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">79
-</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">234
-</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="X19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">736
@@ -3054,7 +3021,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -3070,12 +3037,7 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">534
-</t>
-        </is>
-      </c>
+      <c r="C20" s="2" t="n"/>
       <c r="D20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">268
@@ -3088,15 +3050,10 @@
 </t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
+      <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -3114,7 +3071,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0219
+          <t xml:space="preserve">911
 </t>
         </is>
       </c>
@@ -3126,8 +3083,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>491</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -3138,7 +3094,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -3168,15 +3124,11 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
-</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
+          <t xml:space="preserve">247
+</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr"/>
       <c r="U20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">31
@@ -3227,13 +3179,13 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18246
+          <t xml:space="preserve">12546
 </t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018
+          <t xml:space="preserve">2881
 </t>
         </is>
       </c>
@@ -3251,19 +3203,19 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1711
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -3275,13 +3227,13 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1680
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -3293,7 +3245,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
@@ -3329,13 +3281,13 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">911
+          <t xml:space="preserve">961
 </t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -3407,13 +3359,13 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106 2
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">846
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
@@ -3425,7 +3377,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -3449,13 +3401,13 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
@@ -3479,13 +3431,13 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1236
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -3497,13 +3449,13 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12190
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -3521,7 +3473,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -3537,15 +3489,10 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>364</t>
-        </is>
-      </c>
+      <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -3556,7 +3503,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
@@ -3580,39 +3527,36 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1299
+          <t xml:space="preserve">1290
 </t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">606
 </t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
-</t>
+          <t>9076</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">812
 </t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2691
-</t>
+          <t>469</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3623,7 +3567,7 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -3635,46 +3579,40 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2991
+          <t xml:space="preserve">3931
 </t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
+          <t xml:space="preserve">932
 </t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1100
+          <t xml:space="preserve">1103
 </t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1996
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2100
-</t>
+          <t>7713</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4068
-</t>
-        </is>
-      </c>
-      <c r="Z23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1229
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">416
+</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3689,7 +3627,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23097
+          <t xml:space="preserve">3097
 </t>
         </is>
       </c>
@@ -3701,37 +3639,35 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1701
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2221
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18 051
+          <t xml:space="preserve">1105
 </t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2541
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">9291
 </t>
         </is>
       </c>
@@ -3750,7 +3686,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -3780,14 +3716,13 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2321
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>8746</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3798,26 +3733,26 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211834
+          <t xml:space="preserve">1211834
 </t>
         </is>
       </c>
       <c r="Y24" s="2" t="n"/>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -3857,33 +3792,17 @@
 </t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">79
-</t>
-        </is>
-      </c>
+      <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
-</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">004
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
@@ -3899,32 +3818,27 @@
 </t>
         </is>
       </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+      <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -3966,13 +3880,13 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
@@ -3990,7 +3904,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3414
+          <t xml:space="preserve">3714
 </t>
         </is>
       </c>
@@ -4008,13 +3922,13 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -4026,7 +3940,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8253
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -4038,13 +3952,13 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -4056,31 +3970,30 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">2327
 </t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2416
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -4104,7 +4017,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">1206
 </t>
         </is>
       </c>
@@ -4158,7 +4071,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>46</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -4175,8 +4088,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>4605</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -4193,27 +4105,23 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>464</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">251
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">161
+</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">930
@@ -4222,7 +4130,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
@@ -4234,7 +4142,7 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -4244,14 +4152,10 @@
 </t>
         </is>
       </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>6364</t>
-        </is>
-      </c>
+      <c r="T27" s="2" t="inlineStr"/>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">909
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -4275,7 +4179,7 @@
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">836
+          <t xml:space="preserve">8386
 </t>
         </is>
       </c>
@@ -4311,125 +4215,121 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">250
+</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15 8
+</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1028
+</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">53
+</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">801
+</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">150
 </t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219
-</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1128
-</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">933
-</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8408
+</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">801
+</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2068
+</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1621
+</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">268
 </t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1150
-</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">840
-</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">264
-</t>
-        </is>
-      </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">785
+          <t xml:space="preserve">775
 </t>
         </is>
       </c>
@@ -4453,13 +4353,13 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3436
+          <t xml:space="preserve">23436
 </t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1265
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
@@ -4471,14 +4371,13 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">101 4
 </t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>918</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -4501,24 +4400,28 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">619
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
-</t>
+          <t>466</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr"/>
-      <c r="O29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">865
+</t>
+        </is>
+      </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">26
@@ -4533,19 +4436,19 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -4569,7 +4472,7 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">2069
 </t>
         </is>
       </c>
@@ -4599,61 +4502,50 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1869
-</t>
+          <t>788</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">817
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1121
+</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1004
+          <t xml:space="preserve">609
 </t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7009
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">500
+</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
+          <t xml:space="preserve">1100
 </t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8939
+          <t xml:space="preserve">859
 </t>
         </is>
       </c>
@@ -4665,14 +4557,13 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 10
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14249
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4683,32 +4574,31 @@
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">428
 </t>
         </is>
       </c>
       <c r="R30" s="2" t="n"/>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81094
+          <t xml:space="preserve">21094
 </t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2222
+          <t xml:space="preserve">3222
 </t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">909
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">16818
 </t>
         </is>
       </c>
@@ -4720,20 +4610,14 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9998
-</t>
-        </is>
-      </c>
-      <c r="Y30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1161
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">999
+</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr"/>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
-</t>
+          <t>004</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4756,13 +4640,12 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12862
-</t>
+          <t>963</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1163
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -4774,7 +4657,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111001
+          <t xml:space="preserve">11100
 </t>
         </is>
       </c>
@@ -4786,31 +4669,31 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9 9
+          <t xml:space="preserve">2 9
 </t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11721
+          <t xml:space="preserve">1721
 </t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101208101
+          <t xml:space="preserve">10218101
 </t>
         </is>
       </c>
@@ -4823,7 +4706,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -4835,13 +4718,13 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12 66
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2191
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -4853,13 +4736,13 @@
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">611
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
@@ -4905,15 +4788,10 @@
 </t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">264
-</t>
-        </is>
-      </c>
+      <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1291
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
@@ -4925,31 +4803,31 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1894
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1856
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2014
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -4961,31 +4839,31 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">010
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -4997,37 +4875,37 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12064
+          <t xml:space="preserve">1204
 </t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">1175
 </t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0081
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -5039,7 +4917,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
@@ -5057,7 +4935,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14008
+          <t xml:space="preserve">4008
 </t>
         </is>
       </c>
@@ -5075,13 +4953,13 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
@@ -5093,16 +4971,10 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">241
-</t>
-        </is>
-      </c>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">58
@@ -5117,31 +4989,31 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">018
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2184
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
@@ -5171,13 +5043,13 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1896
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1880
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
@@ -5195,7 +5067,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
@@ -5243,7 +5115,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1156
+          <t xml:space="preserve">1656
 </t>
         </is>
       </c>
@@ -5255,15 +5127,11 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">397
+</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">175
@@ -5272,19 +5140,19 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
@@ -5296,8 +5164,7 @@
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
@@ -5306,12 +5173,7 @@
 </t>
         </is>
       </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">214
-</t>
-        </is>
-      </c>
+      <c r="S34" s="2" t="inlineStr"/>
       <c r="T34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">748
@@ -5320,13 +5182,13 @@
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -5350,7 +5212,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -5410,7 +5272,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
@@ -5428,17 +5290,18 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>450</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -5456,7 +5319,7 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -5474,7 +5337,7 @@
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -5498,13 +5361,13 @@
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
+          <t xml:space="preserve">895
 </t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2441
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
@@ -5552,7 +5415,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
@@ -5564,7 +5427,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
@@ -5589,13 +5452,13 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
@@ -5613,7 +5476,7 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
@@ -5631,13 +5494,13 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">2808
 </t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -5655,7 +5518,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5673,25 +5536,25 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16402
+          <t xml:space="preserve">16452
 </t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16211
+          <t xml:space="preserve">11828
 </t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13011
+          <t xml:space="preserve">16091
 </t>
         </is>
       </c>
@@ -5703,25 +5566,24 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">7106
 </t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1067
+          <t xml:space="preserve">1167
 </t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16006
+          <t xml:space="preserve">1606
 </t>
         </is>
       </c>
@@ -5731,39 +5593,34 @@
 </t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
+      <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
+          <t xml:space="preserve">868
 </t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2980
+          <t xml:space="preserve">2280
 </t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808
+          <t xml:space="preserve">1208
 </t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">18123
 </t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1461
+          <t xml:space="preserve">911
 </t>
         </is>
       </c>
@@ -5775,12 +5632,13 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t xml:space="preserve">2894
+</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1942
+          <t xml:space="preserve">942
 </t>
         </is>
       </c>
@@ -5792,14 +5650,13 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9212
-</t>
-        </is>
-      </c>
-      <c r="X37" s="2" t="n"/>
+          <t>914</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr"/>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44817
+          <t xml:space="preserve">4188
 </t>
         </is>
       </c>
@@ -5816,17 +5673,21 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C38" s="2" t="n"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12928
+</t>
+        </is>
+      </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2631
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8661
-</t>
+          <t>6341</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -5837,13 +5698,13 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">971
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -5855,7 +5716,7 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1231
+          <t xml:space="preserve">331
 </t>
         </is>
       </c>
@@ -5892,13 +5753,12 @@
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2122
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117 8
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -5910,37 +5770,32 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7711
-</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1464
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">771
+</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2086
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">891
+          <t xml:space="preserve">897
 </t>
         </is>
       </c>
@@ -5959,8 +5814,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2864
-</t>
+          <t>9864</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -5977,7 +5831,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -6002,26 +5856,26 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">800
 </t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1077
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="N39" s="2" t="n"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
@@ -6060,7 +5914,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">53590
+          <t xml:space="preserve">3590
 </t>
         </is>
       </c>
@@ -6078,7 +5932,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01116
+          <t xml:space="preserve">01816
 </t>
         </is>
       </c>
@@ -6091,7 +5945,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -6101,7 +5955,12 @@
 </t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">180
@@ -6122,73 +5981,72 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">762
+</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">684
+</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1128
+</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">862
 </t>
         </is>
       </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">614
-</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="W40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="X40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="Y40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">862
-</t>
-        </is>
-      </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
+          <t xml:space="preserve">324
 </t>
         </is>
       </c>
@@ -6206,7 +6064,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>88664</t>
+          <t>48664</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -6223,7 +6081,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
@@ -6231,7 +6089,7 @@
       <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -6244,7 +6102,7 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
@@ -6256,25 +6114,25 @@
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">1260
 </t>
         </is>
       </c>
@@ -6341,7 +6199,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9426
+          <t xml:space="preserve">2426
 </t>
         </is>
       </c>
@@ -6359,7 +6217,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -6371,14 +6229,14 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -6402,7 +6260,7 @@
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -6414,25 +6272,25 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2841
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8299
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
@@ -6442,12 +6300,7 @@
 </t>
         </is>
       </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
+      <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">222
@@ -6462,13 +6315,13 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">897
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
@@ -6490,16 +6343,21 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C43" s="2" t="n"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6
+</t>
+        </is>
+      </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
+          <t xml:space="preserve">1281
 </t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8109
+          <t xml:space="preserve">809
 </t>
         </is>
       </c>
@@ -6511,31 +6369,31 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2211
+          <t xml:space="preserve">525
 </t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0914
+          <t xml:space="preserve">094
 </t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1619
+          <t xml:space="preserve">1618
 </t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -6554,7 +6412,7 @@
       <c r="N43" s="2" t="n"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1055
+          <t xml:space="preserve">4055
 </t>
         </is>
       </c>
@@ -6566,19 +6424,19 @@
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1251
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">1616
 </t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16 16
+          <t xml:space="preserve">10 9
 </t>
         </is>
       </c>
@@ -6590,7 +6448,7 @@
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536
+          <t xml:space="preserve">556
 </t>
         </is>
       </c>
@@ -6600,21 +6458,16 @@
 </t>
         </is>
       </c>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2193
-</t>
-        </is>
-      </c>
+      <c r="W43" s="2" t="inlineStr"/>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201 10
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4 067
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -6716,19 +6569,19 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -6740,7 +6593,7 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">016
 </t>
         </is>
       </c>
@@ -6758,22 +6611,22 @@
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">851
 </t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2028
+</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">208
 </t>
         </is>
       </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">660
@@ -6806,7 +6659,7 @@
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -6838,31 +6691,31 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">014
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
@@ -6886,33 +6739,28 @@
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14107
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
       <c r="R46" s="2" t="inlineStr"/>
       <c r="S46" s="2" t="inlineStr"/>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -6924,22 +6772,17 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="X46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr"/>
       <c r="Y46" s="2" t="n"/>
       <c r="Z46" s="2" t="n"/>
       <c r="AA46" t="inlineStr">

--- a/results/05_transient_transcription_output/905/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/905/Top_Excel_with_OCR_Results.xlsx
@@ -644,13 +644,13 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">825
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -686,19 +686,19 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">0168
 </t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1885
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">2900
 </t>
         </is>
       </c>
@@ -722,7 +722,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1250
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
@@ -734,13 +734,13 @@
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">803
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -756,7 +756,12 @@
 </t>
         </is>
       </c>
-      <c r="Y4" s="2" t="n"/>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">861
+</t>
+        </is>
+      </c>
       <c r="Z4" s="2" t="n"/>
       <c r="AA4" t="inlineStr">
         <is>
@@ -772,13 +777,13 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94326
+          <t xml:space="preserve">4386
 </t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>986</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -789,19 +794,18 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>425</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02150
+          <t xml:space="preserve">1195
 </t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2211
+          <t xml:space="preserve">11210
 </t>
         </is>
       </c>
@@ -819,7 +823,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
@@ -831,19 +835,19 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0176
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">981
+          <t xml:space="preserve">931
 </t>
         </is>
       </c>
@@ -873,13 +877,13 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">743
+          <t xml:space="preserve">843
 </t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
@@ -897,7 +901,7 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
@@ -907,7 +911,12 @@
 </t>
         </is>
       </c>
-      <c r="Z5" s="2" t="n"/>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33
+</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2</t>
@@ -922,7 +931,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4844
+          <t xml:space="preserve">4944
 </t>
         </is>
       </c>
@@ -947,13 +956,13 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">1252
 </t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
@@ -965,7 +974,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -983,11 +992,16 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr"/>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">16
@@ -1032,13 +1046,13 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -1050,7 +1064,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -1072,12 +1086,7 @@
 </t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1281
-</t>
-        </is>
-      </c>
+      <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">162
@@ -1104,13 +1113,14 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">48
+</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1133,13 +1143,14 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">898
+</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1168,7 +1179,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">687
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -1192,19 +1203,19 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
-      <c r="Y7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">900
-</t>
-        </is>
-      </c>
-      <c r="Z7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -1222,7 +1233,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2602
+          <t xml:space="preserve">4602
 </t>
         </is>
       </c>
@@ -1288,7 +1299,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1672
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -1300,7 +1311,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
@@ -1354,13 +1365,13 @@
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">900
+</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">860
-</t>
-        </is>
-      </c>
-      <c r="Z8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -1378,18 +1389,19 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>34405</t>
+          <t xml:space="preserve">22404
+</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18248
+          <t xml:space="preserve">1420
 </t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">8291
 </t>
         </is>
       </c>
@@ -1401,13 +1413,13 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">991
+          <t xml:space="preserve">2591
 </t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">618
+          <t xml:space="preserve">6717
 </t>
         </is>
       </c>
@@ -1431,8 +1443,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
-</t>
+          <t>39801</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1441,15 +1452,10 @@
 </t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
+      <c r="N9" s="2" t="n"/>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">3433
 </t>
         </is>
       </c>
@@ -1461,17 +1467,22 @@
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1271
+          <t xml:space="preserve">12721
 </t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0912
-</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="n"/>
+          <t xml:space="preserve">1109
+</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1243
+</t>
+        </is>
+      </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">3842
@@ -1486,31 +1497,31 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">989
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">927
+</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">638
+</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4451
+</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="X9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1628
-</t>
-        </is>
-      </c>
-      <c r="Y9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4458
-</t>
-        </is>
-      </c>
-      <c r="Z9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1228
 </t>
         </is>
       </c>
@@ -1534,35 +1545,37 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2891
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">1661
 </t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t xml:space="preserve">225
+</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>468</t>
+          <t xml:space="preserve">118
+</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">1185
 </t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2821
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
@@ -1574,27 +1587,23 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1179
 </t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16878
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="n"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">906
@@ -1603,31 +1612,31 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">104 14
 </t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">768
+          <t xml:space="preserve">769
 </t>
         </is>
       </c>
@@ -1639,11 +1648,16 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1981
-</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="n"/>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">206
@@ -1658,7 +1672,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">16 14
 </t>
         </is>
       </c>
@@ -1688,45 +1702,40 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t xml:space="preserve">197
+</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1928
 </t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8311
-</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">172
@@ -1741,7 +1750,8 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>414</t>
+          <t xml:space="preserve">85
+</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1750,27 +1760,22 @@
 </t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">084
-</t>
-        </is>
-      </c>
+      <c r="P11" s="2" t="inlineStr"/>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2163
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
@@ -1782,25 +1787,25 @@
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1106
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">28220
 </t>
         </is>
       </c>
@@ -1872,19 +1877,19 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1814
 </t>
         </is>
       </c>
@@ -1902,7 +1907,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
@@ -1920,18 +1925,19 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">1195
 </t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>086</t>
+          <t xml:space="preserve">2222
+</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9230
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
@@ -1955,7 +1961,7 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -1985,7 +1991,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23238
+          <t xml:space="preserve">3238
 </t>
         </is>
       </c>
@@ -1997,7 +2003,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -2009,7 +2015,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">1105
 </t>
         </is>
       </c>
@@ -2019,13 +2025,13 @@
 </t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1210
+</t>
+        </is>
+      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">140
@@ -2040,18 +2046,28 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">1169
 </t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr"/>
-      <c r="P13" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">922
+</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">244
@@ -2072,13 +2088,13 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -2090,13 +2106,13 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -2144,13 +2160,13 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">28211
 </t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">984
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
@@ -2160,15 +2176,10 @@
 </t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
+      <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">1 2
 </t>
         </is>
       </c>
@@ -2192,7 +2203,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4189
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -2234,7 +2245,7 @@
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -2252,13 +2263,13 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
@@ -2282,7 +2293,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2348
+          <t xml:space="preserve">3348
 </t>
         </is>
       </c>
@@ -2300,25 +2311,25 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">9085
 </t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18 7
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 44 1
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -2330,7 +2341,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">986
 </t>
         </is>
       </c>
@@ -2348,7 +2359,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -2366,7 +2377,7 @@
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
@@ -2378,7 +2389,7 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -2390,7 +2401,7 @@
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
@@ -2420,7 +2431,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -2438,19 +2449,19 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03618
+          <t xml:space="preserve">13618
 </t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">1340
 </t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">856
 </t>
         </is>
       </c>
@@ -2462,13 +2473,13 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24814
+          <t xml:space="preserve">4814
 </t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">730
 </t>
         </is>
       </c>
@@ -2478,33 +2489,40 @@
 </t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">989
+          <t xml:space="preserve">926
 </t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t xml:space="preserve">888
+</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">833
+          <t xml:space="preserve">853
 </t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t xml:space="preserve">14659
+</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2515,47 +2533,49 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">10893
 </t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>71603</t>
+          <t xml:space="preserve">1043
+</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11 29
+          <t xml:space="preserve">21166
 </t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>415</t>
+          <t xml:space="preserve">1998
+</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">831
+          <t xml:space="preserve">351
 </t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1018
+          <t xml:space="preserve">1019
 </t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">869
+          <t xml:space="preserve">9691
 </t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">0987
 </t>
         </is>
       </c>
@@ -2565,12 +2585,7 @@
 </t>
         </is>
       </c>
-      <c r="Z16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
+      <c r="Z16" s="2" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2585,13 +2600,13 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3124
+          <t xml:space="preserve">23124
 </t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1601
+          <t xml:space="preserve">9401
 </t>
         </is>
       </c>
@@ -2603,11 +2618,16 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="n"/>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">297
+</t>
+        </is>
+      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">146
@@ -2616,7 +2636,8 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4816</t>
+          <t xml:space="preserve">22
+</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2627,40 +2648,40 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">4
+</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">932
+</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">14
 </t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">932
-</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">141
-</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">239
@@ -2669,19 +2690,19 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2691
+          <t xml:space="preserve">21891
 </t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2298
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1887
+          <t xml:space="preserve">7891
 </t>
         </is>
       </c>
@@ -2693,25 +2714,25 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">12116
 </t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1294
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">28 12 1
 </t>
         </is>
       </c>
@@ -2735,7 +2756,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2546
+          <t xml:space="preserve">3546
 </t>
         </is>
       </c>
@@ -2751,10 +2772,15 @@
 </t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2909
+</t>
+        </is>
+      </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1867
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -2766,7 +2792,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2776,13 +2802,13 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -2794,7 +2820,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -2812,13 +2838,13 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>8491</t>
+          <t xml:space="preserve">218
+</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
@@ -2835,37 +2861,37 @@
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1418
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">224 884
+</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11 11
+</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">209
 </t>
         </is>
       </c>
-      <c r="W18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="X18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">267
-</t>
-        </is>
-      </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
@@ -2883,7 +2909,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">2194
 </t>
         </is>
       </c>
@@ -2901,7 +2927,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2088
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -2913,13 +2939,13 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -2931,7 +2957,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -2943,13 +2969,13 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">874
 </t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -2961,7 +2987,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8881
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -2973,13 +2999,13 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">2086
 </t>
         </is>
       </c>
@@ -2991,7 +3017,7 @@
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -3015,13 +3041,13 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">736
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
@@ -3037,10 +3063,14 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n"/>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>3588</t>
+        </is>
+      </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">9268
 </t>
         </is>
       </c>
@@ -3050,7 +3080,12 @@
 </t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">90
@@ -3065,25 +3100,25 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">911
+          <t xml:space="preserve">531
 </t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>491</t>
+          <t xml:space="preserve">182
+</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -3094,7 +3129,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -3124,11 +3159,16 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1247
+</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18918
+</t>
+        </is>
+      </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">31
@@ -3179,14 +3219,13 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12546
+          <t xml:space="preserve">22842
 </t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2881
-</t>
+          <t>681</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -3203,19 +3242,19 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">1718
 </t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -3227,7 +3266,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -3245,7 +3284,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3261,12 +3300,7 @@
 </t>
         </is>
       </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
       <c r="R21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">199
@@ -3281,13 +3315,13 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">961
+          <t xml:space="preserve">911
 </t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -3341,7 +3375,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">976
 </t>
         </is>
       </c>
@@ -3353,7 +3387,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">923
 </t>
         </is>
       </c>
@@ -3377,7 +3411,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
@@ -3389,7 +3423,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -3401,7 +3435,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -3437,7 +3471,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">7240
 </t>
         </is>
       </c>
@@ -3473,7 +3507,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
@@ -3489,10 +3523,16 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="2" t="n"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15426
+</t>
+        </is>
+      </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t xml:space="preserve">1376
+</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -3503,19 +3543,19 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
+          <t xml:space="preserve">3526
 </t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">748
 </t>
         </is>
       </c>
@@ -3527,65 +3567,56 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1290
+          <t xml:space="preserve">1193
 </t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">606
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>9076</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr"/>
+          <t xml:space="preserve">878
+</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9
+</t>
+        </is>
+      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
           <t>469</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81158
+          <t xml:space="preserve">2158
 </t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3931
+          <t xml:space="preserve">2931
 </t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">932
+          <t xml:space="preserve">332
 </t>
         </is>
       </c>
@@ -3597,22 +3628,28 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>7713</t>
+          <t xml:space="preserve">1109
+</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">416
-</t>
-        </is>
-      </c>
-      <c r="Z23" s="2" t="inlineStr"/>
+          <t xml:space="preserve">6068
+</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3639,60 +3676,66 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t xml:space="preserve">1701
+</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">292
+</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1105
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">11848
 </t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9291
-</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr"/>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>481</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1741
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9381
+          <t xml:space="preserve">938
 </t>
         </is>
       </c>
@@ -3716,13 +3759,14 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>8746</t>
+          <t xml:space="preserve">787
+</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3733,7 +3777,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
@@ -3745,14 +3789,19 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1211834
-</t>
-        </is>
-      </c>
-      <c r="Y24" s="2" t="n"/>
+          <t xml:space="preserve">881811
+</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">824
+</t>
+        </is>
+      </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
@@ -3770,8 +3819,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2798
-</t>
+          <t>4799</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3792,17 +3840,23 @@
 </t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">75
+</t>
+        </is>
+      </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>156</t>
+          <t xml:space="preserve">156
+</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
@@ -3814,11 +3868,11 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1182
+</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="n"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
           <t>94</t>
@@ -3826,19 +3880,19 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -3856,37 +3910,37 @@
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">5117
+</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5514
+</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2544
+</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">211
 </t>
         </is>
       </c>
-      <c r="W25" s="2" t="inlineStr">
+      <c r="Z25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="X25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="Y25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="Z25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">163
 </t>
         </is>
       </c>
@@ -3904,7 +3958,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3714
+          <t xml:space="preserve">3411
 </t>
         </is>
       </c>
@@ -3922,19 +3976,19 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -3946,13 +4000,13 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -3970,13 +4024,14 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>970</t>
+          <t xml:space="preserve">970
+</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3987,7 +4042,7 @@
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2327
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
@@ -3999,7 +4054,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
@@ -4029,7 +4084,7 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
@@ -4071,7 +4126,8 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t xml:space="preserve">167
+</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -4088,7 +4144,8 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4605</t>
+          <t xml:space="preserve">160
+</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -4105,13 +4162,13 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -4121,7 +4178,12 @@
 </t>
         </is>
       </c>
-      <c r="N27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">930
@@ -4148,11 +4210,16 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr"/>
+          <t xml:space="preserve">227
+</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">696
+</t>
+        </is>
+      </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">99
@@ -4173,13 +4240,13 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">1207
 </t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8386
+          <t xml:space="preserve">836
 </t>
         </is>
       </c>
@@ -4203,7 +4270,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4536
+          <t xml:space="preserve">453
 </t>
         </is>
       </c>
@@ -4213,12 +4280,7 @@
 </t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
-      </c>
+      <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">219
@@ -4227,19 +4289,20 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15 8
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1028
+          <t xml:space="preserve">1128
 </t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t xml:space="preserve">33
+</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -4250,49 +4313,48 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">801
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>461</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8408
+          <t xml:space="preserve">8406
 </t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">801
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2068
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -4302,10 +4364,15 @@
 </t>
         </is>
       </c>
-      <c r="T28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">747
+</t>
+        </is>
+      </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1621
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -4317,13 +4384,13 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">28641
 </t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -4335,7 +4402,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
@@ -4353,7 +4420,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23436
+          <t xml:space="preserve">3436
 </t>
         </is>
       </c>
@@ -4365,19 +4432,20 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101 4
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>918</t>
+          <t xml:space="preserve">98
+</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -4394,70 +4462,76 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">41
+</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">865
+</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8216
+</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">815
+</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">48
 </t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>466</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr"/>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">865
-</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">208
@@ -4472,7 +4546,7 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -4502,19 +4576,25 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>788</t>
+          <t xml:space="preserve">1788
+</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
-</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1384
+</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">814
+</t>
+        </is>
+      </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">609
+          <t xml:space="preserve">1064
 </t>
         </is>
       </c>
@@ -4524,10 +4604,15 @@
 </t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7107
+</t>
+        </is>
+      </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1100
+          <t xml:space="preserve">1890
 </t>
         </is>
       </c>
@@ -4557,31 +4642,37 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">14345
+</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">5 82
 </t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">428
-</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="n"/>
+          <t xml:space="preserve">1142
+</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2002
+</t>
+        </is>
+      </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21094
+          <t xml:space="preserve">1094
 </t>
         </is>
       </c>
@@ -4593,31 +4684,38 @@
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>303</t>
+          <t xml:space="preserve">2303
+</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16818
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">1918
 </t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">999
-</t>
-        </is>
-      </c>
-      <c r="Y30" s="2" t="inlineStr"/>
+          <t xml:space="preserve">9981
+</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4161
+</t>
+        </is>
+      </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>004</t>
+          <t xml:space="preserve">200
+</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4634,30 +4732,31 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23577
+          <t xml:space="preserve">3577
 </t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>963</t>
+          <t xml:space="preserve">9631
+</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11100
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -4669,44 +4768,44 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">8961
 </t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 9
+          <t xml:space="preserve">28 9
 </t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1721
+          <t xml:space="preserve">13721
 </t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10218101
+          <t xml:space="preserve">1662
 </t>
         </is>
       </c>
       <c r="N31" s="2" t="n"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">909
+          <t xml:space="preserve">4 90
 </t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -4718,7 +4817,7 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
@@ -4730,7 +4829,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">784
+          <t xml:space="preserve">704
 </t>
         </is>
       </c>
@@ -4742,31 +4841,31 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1841
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">401
+          <t xml:space="preserve">851
 </t>
         </is>
       </c>
@@ -4784,86 +4883,69 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2666
-</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr"/>
+          <t>9566</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">1171
 </t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">21 7
 </t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">13 118
 </t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">214
-</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">89
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="n"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">220
 </t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
+      <c r="P32" s="2" t="inlineStr"/>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1183
 </t>
         </is>
       </c>
@@ -4875,7 +4957,7 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1204
+          <t xml:space="preserve">184415 18
 </t>
         </is>
       </c>
@@ -4887,37 +4969,37 @@
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1169
+</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">940
+</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">1175
-</t>
-        </is>
-      </c>
-      <c r="W32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="X32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="Y32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">940
-</t>
-        </is>
-      </c>
-      <c r="Z32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211
 </t>
         </is>
       </c>
@@ -4953,7 +5035,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">2251
 </t>
         </is>
       </c>
@@ -4971,10 +5053,15 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr"/>
+          <t>861</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">58
@@ -4989,25 +5076,25 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">780
 </t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
@@ -5037,13 +5124,13 @@
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>
@@ -5061,13 +5148,13 @@
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
+          <t xml:space="preserve">2865
 </t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -5085,7 +5172,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23502
+          <t xml:space="preserve">3502
 </t>
         </is>
       </c>
@@ -5109,50 +5196,55 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1656
+          <t xml:space="preserve">1156
 </t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">97
+</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1166
+</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">18
 </t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">397
-</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">175
-</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
@@ -5164,7 +5256,8 @@
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t xml:space="preserve">293
+</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
@@ -5173,7 +5266,12 @@
 </t>
         </is>
       </c>
-      <c r="S34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">748
@@ -5182,7 +5280,7 @@
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
@@ -5212,7 +5310,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -5254,7 +5352,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -5284,24 +5382,25 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">1886
 </t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t xml:space="preserve">18
+</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">800
 </t>
         </is>
       </c>
@@ -5319,46 +5418,46 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1281
+</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">860
+</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">67
+</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">211
 </t>
         </is>
       </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">860
-</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="W35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="X35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">895
@@ -5367,7 +5466,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -5385,7 +5484,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3568
+          <t xml:space="preserve">356
 </t>
         </is>
       </c>
@@ -5415,7 +5514,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">1134
 </t>
         </is>
       </c>
@@ -5427,7 +5526,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
@@ -5449,10 +5548,15 @@
 </t>
         </is>
       </c>
-      <c r="N36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
@@ -5482,7 +5586,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">602
+          <t xml:space="preserve">1682
 </t>
         </is>
       </c>
@@ -5494,13 +5598,13 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2808
+          <t xml:space="preserve">8208
 </t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -5518,7 +5622,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">418
 </t>
         </is>
       </c>
@@ -5536,25 +5640,25 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16452
+          <t xml:space="preserve">1643
 </t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11828
+          <t xml:space="preserve">2314
 </t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">829
 </t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16091
+          <t xml:space="preserve">1071
 </t>
         </is>
       </c>
@@ -5572,95 +5676,101 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1167
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1606
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t xml:space="preserve">885
+</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2280
+          <t xml:space="preserve">8998
 </t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
+          <t xml:space="preserve">0120
 </t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18123
+          <t xml:space="preserve">2229
 </t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">911
+          <t xml:space="preserve">991
 </t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1008
+          <t xml:space="preserve">1038
 </t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2894
+          <t xml:space="preserve">93834
 </t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">942
-</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">981
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">342
+</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr"/>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>914</t>
-        </is>
-      </c>
-      <c r="X37" s="2" t="inlineStr"/>
+          <t xml:space="preserve">9231
+</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">029
+</t>
+        </is>
+      </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4188
-</t>
-        </is>
-      </c>
-      <c r="Z37" s="2" t="n"/>
+          <t xml:space="preserve">2187
+</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -5675,30 +5785,31 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12928
+          <t xml:space="preserve">3296
 </t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>6341</t>
+          <t xml:space="preserve">1661
+</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
@@ -5708,40 +5819,40 @@
 </t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
+      <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">331
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">16889
 </t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="n"/>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7961
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
@@ -5753,18 +5864,19 @@
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">02251
+</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">20971
 </t>
         </is>
       </c>
@@ -5774,32 +5886,42 @@
 </t>
         </is>
       </c>
-      <c r="U38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">1904
 </t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">1898
 </t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">2005
 </t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">897
-</t>
-        </is>
-      </c>
-      <c r="Z38" s="2" t="n"/>
+          <t xml:space="preserve">89718
+</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -5814,92 +5936,120 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>9864</t>
+          <t xml:space="preserve">2644
+</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>854</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="n"/>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>331</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="n"/>
+          <t xml:space="preserve">1178
+</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">850
+</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr"/>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="R39" s="2" t="n"/>
-      <c r="S39" s="2" t="n"/>
-      <c r="T39" s="2" t="n"/>
-      <c r="U39" s="2" t="n"/>
-      <c r="V39" s="2" t="n"/>
-      <c r="W39" s="2" t="n"/>
-      <c r="X39" s="2" t="n"/>
-      <c r="Y39" s="2" t="n"/>
-      <c r="Z39" s="2" t="n"/>
+          <t xml:space="preserve">298
+</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1222
+</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231
+</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">889
+</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr"/>
       <c r="AA39" t="inlineStr">
         <is>
           <t>26</t>
@@ -5914,56 +6064,61 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3590
+          <t xml:space="preserve">2864
 </t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01816
-</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="n"/>
+          <t xml:space="preserve">287
+</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1079
 </t>
         </is>
       </c>
@@ -5975,78 +6130,79 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">762
+          <t xml:space="preserve">825
 </t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">1207
 </t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">684
+          <t xml:space="preserve">744
 </t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">200
+</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
+          <t xml:space="preserve">897
 </t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
@@ -6064,124 +6220,138 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>48664</t>
+          <t xml:space="preserve">3590
+</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>515</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="n"/>
-      <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="n"/>
+          <t xml:space="preserve">205
+</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10169
+</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1138
+</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
+          <t xml:space="preserve">1553
 </t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">762
 </t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">2094
 </t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">579
+          <t xml:space="preserve">614
 </t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
-        </is>
-      </c>
-      <c r="W41" s="2" t="inlineStr"/>
+          <t>044</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">734
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
@@ -6199,44 +6369,43 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2426
-</t>
+          <t>48561</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">63
 </t>
         </is>
       </c>
@@ -6248,7 +6417,7 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
@@ -6260,68 +6429,73 @@
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">798
+          <t xml:space="preserve">6820
 </t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">579
+</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">141
+</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">233
+</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">202
 </t>
         </is>
       </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">899
-</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">555
-</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr"/>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="W42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="X42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
@@ -6345,129 +6519,134 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
+          <t xml:space="preserve">7426
 </t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1281
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">809
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1081
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">525
+          <t xml:space="preserve">2885
 </t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">094
-</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1618
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
+          <t xml:space="preserve">1880
 </t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">796
-</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="n"/>
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4055
+          <t xml:space="preserve">798
 </t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1616
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10 9
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">555
 </t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">556
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1048
-</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="inlineStr"/>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">2185
 </t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
@@ -6527,143 +6706,143 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3629
+          <t xml:space="preserve">18890
 </t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1344
+</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr"/>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">1081
 </t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">595
 </t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">697
 </t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">1174
 </t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">861
 </t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">909
 </t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15 9
+          <t xml:space="preserve">537
 </t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">016
+          <t xml:space="preserve">710
 </t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">14055
 </t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">851
+          <t xml:space="preserve">12684
 </t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028
+          <t xml:space="preserve">1018
 </t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">1048
 </t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
+          <t xml:space="preserve">3300
 </t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">556
 </t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">1048
 </t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">985
 </t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="Z45" s="2" t="n"/>
+          <t xml:space="preserve">1088
+</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -6676,115 +6855,149 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3629
+</t>
+        </is>
+      </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">816
+</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>4398</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">85
+</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52
+</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1659
+</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">811
+</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">251
+</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">809
+</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">814
+</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">1
 </t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr"/>
-      <c r="R46" s="2" t="inlineStr"/>
-      <c r="S46" s="2" t="inlineStr"/>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="U46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="X46" s="2" t="inlineStr"/>
-      <c r="Y46" s="2" t="n"/>
-      <c r="Z46" s="2" t="n"/>
+          <t xml:space="preserve">4
+</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/905/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/905/Top_Excel_with_OCR_Results.xlsx
@@ -626,140 +626,117 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3898
-</t>
+          <t>3898</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">883
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">851
-</t>
+          <t>851</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">861
-</t>
+          <t>861</t>
         </is>
       </c>
       <c r="Z4" s="2" t="n"/>
@@ -777,8 +754,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4386
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -788,8 +764,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -799,122 +774,102 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11210
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">931
-</t>
+          <t>931</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">843
-</t>
+          <t>743</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -931,141 +886,118 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4944
-</t>
+          <t>4844</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1252
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">690
-</t>
+          <t>690</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1082,141 +1014,118 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3844
-</t>
+          <t>3744</t>
         </is>
       </c>
       <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
-</t>
+          <t>898</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>687</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1233,146 +1142,122 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4602
-</t>
+          <t>602</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
-</t>
+          <t>882</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">871
-</t>
+          <t>871</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
-</t>
+          <t>860</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1389,56 +1274,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22404
-</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1420
-</t>
+          <t>1420</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8291
-</t>
+          <t>8291</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2591
-</t>
+          <t>591</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6717
-</t>
+          <t>677</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1448,81 +1324,68 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">845
-</t>
+          <t>845</t>
         </is>
       </c>
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3433
-</t>
+          <t>3453</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12721
-</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
-</t>
+          <t>1109</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
-</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3842
-</t>
+          <t>3842</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">385
-</t>
+          <t>385</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>989</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">927
-</t>
+          <t>927</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">638
-</t>
+          <t>031</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4451
-</t>
+          <t>4451</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,141 +1402,118 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4281
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1661
-</t>
+          <t>1661</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1185
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="N10" s="2" t="n"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
-</t>
+          <t>906</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104 14
-</t>
+          <t>101 14</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">769
-</t>
+          <t>768</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
-</t>
+          <t>77</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16 14
-</t>
+          <t>21 14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1690,44 +1530,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2996
-</t>
+          <t>2996</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1928
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1738,87 +1571,73 @@
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr"/>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">684
-</t>
+          <t>684</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">845
-</t>
+          <t>845</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1835,146 +1654,122 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3436
-</t>
+          <t>3436</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1814
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
-</t>
+          <t>921</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">891
-</t>
+          <t>891</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1991,141 +1786,118 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3238
-</t>
+          <t>3238</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>775</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">958
-</t>
+          <t>958</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2142,141 +1914,118 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2600
-</t>
+          <t>2600</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 2
-</t>
+          <t>21 2</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">896
-</t>
+          <t>896</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">956
-</t>
+          <t>956</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2293,146 +2042,122 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3348
-</t>
+          <t>8348</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9085
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
-</t>
+          <t>940</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">593
-</t>
+          <t>593</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2449,140 +2174,117 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13618
-</t>
+          <t>15618</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1340
-</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">856
-</t>
+          <t>856</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1099
-</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4814
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
-</t>
+          <t>730</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
+          <t>888</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">853
-</t>
+          <t>853</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14659
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10893
-</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1043
-</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21166
-</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1998
-</t>
+          <t>3938</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">351
-</t>
+          <t>351</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1019
-</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9691
-</t>
+          <t>969</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0987
-</t>
+          <t>097</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4584
-</t>
+          <t>4574</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr"/>
@@ -2600,146 +2302,122 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23124
-</t>
+          <t>3124</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9401
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
-</t>
+          <t>297</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">932
-</t>
+          <t>932</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21891
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7891
-</t>
+          <t>788</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12116
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28 12 1
-</t>
+          <t>28 8 1</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2756,38 +2434,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3546
-</t>
+          <t>3546</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
-</t>
+          <t>277</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2909
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2802,38 +2474,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
-</t>
+          <t>871</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2843,56 +2509,47 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1665
-</t>
+          <t>665</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224 884
-</t>
+          <t>224 214</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11 11
-</t>
+          <t>28 12</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2909,146 +2566,122 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
-</t>
+          <t>940</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2086
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>731</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>736</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3070,32 +2703,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -3105,104 +2733,87 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">531
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18918
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
-</t>
+          <t>938</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3219,8 +2830,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22842
-</t>
+          <t>2846</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3230,129 +2840,108 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1718
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
-</t>
+          <t>940</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr"/>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">911
-</t>
+          <t>911</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
-</t>
+          <t>968</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3369,146 +2958,122 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3392
-</t>
+          <t>3392</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">976
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">923
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7240
-</t>
+          <t>740</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">691
-</t>
+          <t>691</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3525,56 +3090,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15426
-</t>
+          <t>15486</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1376
-</t>
+          <t>1376</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3526
-</t>
+          <t>526</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">748
-</t>
+          <t>742</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -3584,14 +3140,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
-</t>
+          <t>872</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -3604,50 +3158,42 @@
       <c r="R23" s="2" t="inlineStr"/>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2158
-</t>
+          <t>1158</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2931
-</t>
+          <t>937</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
-</t>
+          <t>332</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
-</t>
+          <t>1103</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
-</t>
+          <t>996</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
-</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6068
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3664,56 +3210,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3097
-</t>
+          <t>3097</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1701
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11848
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3723,86 +3260,72 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
-</t>
+          <t>938</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2391
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2101
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">787
-</t>
+          <t>787</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">881811
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">824
-</t>
+          <t>834</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3824,52 +3347,44 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="N25" s="2" t="n"/>
@@ -3880,68 +3395,57 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">825
-</t>
+          <t>825</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5117
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5514
-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2544
-</t>
+          <t>555</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3958,146 +3462,122 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3411
-</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
-</t>
+          <t>839</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4114,146 +3594,122 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700
-</t>
+          <t>3700</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">696
-</t>
+          <t>696</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">836
-</t>
+          <t>836</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4270,51 +3726,43 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">453
-</t>
+          <t>4536</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -4324,86 +3772,72 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8406
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">747
-</t>
+          <t>747</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28641
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">775
-</t>
+          <t>775</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4420,146 +3854,122 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3436
-</t>
+          <t>3436</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">865
-</t>
+          <t>865</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
-</t>
+          <t>815</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
+          <t>880</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4576,146 +3986,122 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1788
-</t>
+          <t>17884</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1384
-</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1064
-</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
-</t>
+          <t>500</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7107
-</t>
+          <t>707</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1890
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
-</t>
+          <t>859</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
+          <t>812</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14345
-</t>
+          <t>4545</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 82
-</t>
+          <t>2 89</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
-</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2002
-</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1094
-</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3222
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2303
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
-</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1918
-</t>
+          <t>918</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9981
-</t>
+          <t>999</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4732,141 +4118,118 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3577
-</t>
+          <t>3577</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9631
-</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8961
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28 9
-</t>
+          <t>8 9</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13721
-</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1662
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="N31" s="2" t="n"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4 90
-</t>
+          <t>12 90</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">704
-</t>
+          <t>784</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">851
-</t>
+          <t>832</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4888,38 +4251,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21 7
-</t>
+          <t>21 7</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>93</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13 118
-</t>
+          <t>13 15</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
@@ -4931,76 +4288,64 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="N32" s="2" t="n"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>720</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr"/>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184415 18
-</t>
+          <t>158 8</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
-</t>
+          <t>940</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -5017,38 +4362,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4008
-</t>
+          <t>4008</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2251
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -5058,104 +4397,87 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">780
-</t>
+          <t>780</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">774
-</t>
+          <t>774</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2865
-</t>
+          <t>860</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5172,146 +4494,122 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3502
-</t>
+          <t>3502</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">748
-</t>
+          <t>748</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5328,146 +4626,122 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2688
-</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1886
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1281
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
-</t>
+          <t>760</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
-</t>
+          <t>67</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">895
-</t>
+          <t>895</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5484,146 +4758,122 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">356
-</t>
+          <t>3568</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>770</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1682
-</t>
+          <t>602</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8208
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
-</t>
+          <t>952</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">418
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5640,44 +4890,37 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1643
-</t>
+          <t>6432</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2314
-</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
-</t>
+          <t>829</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1071
-</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">485
-</t>
+          <t>485</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7106
-</t>
+          <t>706</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
@@ -5688,87 +4931,73 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
-</t>
+          <t>883</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>770</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8998
-</t>
+          <t>398</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0120
-</t>
+          <t>020</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2229
-</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">991
-</t>
+          <t>971</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1038
-</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93834
-</t>
+          <t>3854</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">342
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr"/>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">029
-</t>
+          <t>029</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2187
-</t>
+          <t>487</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5785,141 +5014,118 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3296
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1661
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16889
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02251
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20971
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">771
-</t>
+          <t>771</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1904
-</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1898
-</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2005
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89718
-</t>
+          <t>897</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5936,8 +5142,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2644
-</t>
+          <t>2644</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -5947,27 +5152,23 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -5977,8 +5178,7 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -5988,65 +5188,55 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr"/>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr"/>
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
-</t>
+          <t>889</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr"/>
@@ -6064,146 +5254,122 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2864
-</t>
+          <t>2864</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1079
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">825
-</t>
+          <t>825</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">744
-</t>
+          <t>744</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">897
-</t>
+          <t>897</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6220,8 +5386,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3590
-</t>
+          <t>3590</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -6231,99 +5396,83 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10169
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1553
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">762
-</t>
+          <t>762</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2094
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">614
-</t>
+          <t>614</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
@@ -6333,26 +5482,22 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
+          <t>862</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6374,135 +5519,113 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
-</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6820
-</t>
+          <t>620</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">579
-</t>
+          <t>579</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>705</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6519,135 +5642,113 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7426
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2885
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1880
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">798
-</t>
+          <t>798</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">555
-</t>
+          <t>555</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2185
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Z43" s="2" t="n"/>
@@ -6665,8 +5766,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D44" s="2" t="n"/>
@@ -6706,141 +5806,118 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18890
-</t>
+          <t>8390</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1344
-</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1081
-</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">595
-</t>
+          <t>525</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">697
-</t>
+          <t>697</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">861
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">909
-</t>
+          <t>902</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">537
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14055
-</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12684
-</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1018
-</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1048
-</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3300
-</t>
+          <t>3300</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">556
-</t>
+          <t>556</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1048
-</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">985
-</t>
+          <t>935</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
+          <t>012</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1088
-</t>
+          <t>087</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6857,32 +5934,27 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3629
-</t>
+          <t>3679</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -6892,110 +5964,92 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1659
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
-</t>
+          <t>811</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">809
-</t>
+          <t>800</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">

--- a/results/05_transient_transcription_output/905/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/905/Top_Excel_with_OCR_Results.xlsx
@@ -681,7 +681,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>118</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>190</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>228</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>4602</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>224</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>212</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>21404</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1661</t>
+          <t>166</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>101 14</t>
+          <t>01 214 1</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>21 14</t>
+          <t>181 14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>21 2</t>
+          <t>1 21 2</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>118</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8348</t>
+          <t>3348</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>118</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>160</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>484</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>99</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>4659</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2377,17 +2377,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>7881</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>28 8 1</t>
+          <t>20 2 2</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>118</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2529,12 +2529,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>224 214</t>
+          <t>226 214</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28 12</t>
+          <t>14 214</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>3194</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>195</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>282</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>140</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>280</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>1112</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>99</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>3937</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>11034</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>221</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2281</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
@@ -3425,17 +3425,17 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>2114</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>214</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>2624</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>282</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>47</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>282</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>184</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>8141</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>288</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>88</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>1161</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -4123,7 +4123,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>2631</t>
+          <t>264</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -4148,17 +4148,17 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>261</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>8 9</t>
+          <t>3 9</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -4174,7 +4174,7 @@
       <c r="N31" s="2" t="n"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12 90</t>
+          <t>21 90</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>204</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>211</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>13 15</t>
+          <t>13 01</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>158 8</t>
+          <t>2611 4</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>183</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>176</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>102</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>800</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4813,7 +4813,7 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>191</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>6432</t>
+          <t>16432</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>8398</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4976,28 +4976,28 @@
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>342</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr"/>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>9231</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>029</t>
+          <t>0294</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>1487</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>3286</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>116</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>2081</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
@@ -5105,27 +5105,27 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>196</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>183</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>206</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>891</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>222</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
@@ -5269,7 +5269,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>267</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
@@ -5565,7 +5565,7 @@
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>26</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>36</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -5693,7 +5693,7 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>734</t>
         </is>
       </c>
       <c r="Z43" s="2" t="n"/>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>8390</t>
+          <t>18390</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5852,12 +5852,12 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>237</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>116</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
@@ -5907,17 +5907,17 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>212</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>087</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>214</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>105</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>011</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -6009,17 +6009,17 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>208</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>011</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>114</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>04</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">

--- a/results/05_transient_transcription_output/905/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/905/Top_Excel_with_OCR_Results.xlsx
@@ -681,7 +681,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3744</t>
+          <t>374</t>
         </is>
       </c>
       <c r="D7" s="2" t="n"/>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>898</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>284</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21404</t>
+          <t>2140</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>1124</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>031</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1473,12 +1473,12 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>20</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>01 214 1</t>
+          <t>04 20</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>181 14</t>
+          <t>00 04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>09</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1 21 2</t>
+          <t>21 2</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>95</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>97</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7881</t>
+          <t>788</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>20 2 2</t>
+          <t>20 0 1</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2529,12 +2529,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>226 214</t>
+          <t>800 00</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14 214</t>
+          <t>18 20</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>890</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>178</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>840</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>200</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1112</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>91</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>11034</t>
+          <t>1103</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>1168</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>2281</t>
+          <t>228</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
@@ -3425,17 +3425,17 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>20</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>200</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>170</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>840</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>184</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>17884</t>
+          <t>1788</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>8141</t>
+          <t>814</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>859</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2 89</t>
+          <t>8 89</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>392</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>208</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -4123,7 +4123,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>263</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>172</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>00</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>13 01</t>
+          <t>13 00</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2611 4</t>
+          <t>000 2</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -4813,7 +4813,7 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>208</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>187</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4982,12 +4982,12 @@
       <c r="V37" s="2" t="inlineStr"/>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>9231</t>
+          <t>923</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>0294</t>
+          <t>029</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>28</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2081</t>
+          <t>208</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
@@ -5269,7 +5269,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>207</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
@@ -5565,12 +5565,12 @@
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>820</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>9426</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -5693,7 +5693,7 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D44" s="2" t="n"/>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>18390</t>
+          <t>1890</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>896</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
@@ -5877,12 +5877,12 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
@@ -5907,17 +5907,17 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>288</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>10887</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>011</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -6014,17 +6014,17 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>10</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
